--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.1%</t>
+          <t>-591.0%</t>
         </is>
       </c>
     </row>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.294938230594427</v>
+        <v>-4.294763650564169</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9731715974824309</v>
+        <v>0.973241429494534</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3952714393104365</v>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>132.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.4%</t>
+          <t>445.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.0%</t>
+          <t>-574.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.9%</t>
+          <t>-272.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-117.1%</t>
+          <t>-1017.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-263.5%</t>
+          <t>-259.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-200.6%</t>
+          <t>-197.9%</t>
         </is>
       </c>
     </row>
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.29838598894274</v>
+        <v>-10.13391361967919</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.982284283957167</v>
+        <v>-0.9164953362517476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.364488512853932</v>
+        <v>-2.319584068347235</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.718733428221316</v>
+        <v>1.745676094925334</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.51642376057391</v>
+        <v>-10.35195139131037</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.065016838125203</v>
+        <v>-0.9992278904197822</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.539259280949831</v>
+        <v>-2.494354836443134</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.618353521848213</v>
+        <v>1.645296188552231</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.44295392890647</v>
+        <v>-10.27848155964292</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.020257203964801</v>
+        <v>-0.954468256259382</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.465789449282382</v>
+        <v>-2.420885004775686</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.677807122342103</v>
+        <v>1.704749789046121</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.61807834629301</v>
+        <v>-10.45360597702946</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.075751750171902</v>
+        <v>-1.009962802466482</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.640913866668926</v>
+        <v>-2.59600942216223</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.587287692657693</v>
+        <v>1.614230359361711</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.8525304403075</v>
+        <v>-10.68805807104395</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.176751752679294</v>
+        <v>-1.110962804973874</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.640913866668926</v>
+        <v>-2.59600942216223</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.580068527756097</v>
+        <v>1.607011194460115</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.14033428484474</v>
+        <v>-10.97586191558119</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.298545481268166</v>
+        <v>-1.232756533562746</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.928717711206164</v>
+        <v>-2.883813266699468</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.400714030259778</v>
+        <v>1.427656696963796</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.37015873200856</v>
+        <v>-11.20568636274501</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.38935947029514</v>
+        <v>-1.323570522589719</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.091365248276325</v>
+        <v>-3.046460803769628</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.304241297856238</v>
+        <v>1.331183964560256</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.60218765174482</v>
+        <v>-11.43771528248127</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.47947730956053</v>
+        <v>-1.413688361855109</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.153377945464748</v>
+        <v>-3.108473500958052</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.269727408172299</v>
+        <v>1.296670074876317</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.55017213777601</v>
+        <v>-11.38569976851246</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.454680768286603</v>
+        <v>-1.388891820581184</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.153377945464748</v>
+        <v>-3.108473500958052</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.2737177438587</v>
+        <v>1.300660410562718</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.69184397950013</v>
+        <v>-11.52737161023658</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.512824731874993</v>
+        <v>-1.447035784169573</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.153377945464748</v>
+        <v>-3.108473500958052</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.272242516959958</v>
+        <v>1.299185183663976</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.6422531350753</v>
+        <v>-11.47778076581175</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.477934983940187</v>
+        <v>-1.412146036234768</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.103787101039914</v>
+        <v>-3.058882656533218</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.317050433779731</v>
+        <v>1.343993100483749</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.4431010278382</v>
+        <v>-11.27862865857465</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.41132527469203</v>
+        <v>-1.345536326986611</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.938464575090101</v>
+        <v>-2.893560130583404</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.403192815702936</v>
+        <v>1.430135482406954</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.21725587511879</v>
+        <v>-11.05278350585524</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.311408140568058</v>
+        <v>-1.245619192862638</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.896537899502937</v>
+        <v>-2.851633454996241</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.437927894091443</v>
+        <v>1.46487056079546</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.0926772187812</v>
+        <v>-10.92820484951765</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.260437533476962</v>
+        <v>-1.194648585771543</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.896537899502937</v>
+        <v>-2.851633454996241</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.439067038647502</v>
+        <v>1.466009705351519</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.14557250682548</v>
+        <v>-10.98110013756193</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.278961874532569</v>
+        <v>-1.213172926827149</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.891582553414491</v>
+        <v>-2.846678108907795</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.444674020462677</v>
+        <v>1.471616687166695</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.86166377589673</v>
+        <v>-10.69719140663318</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.159664677922433</v>
+        <v>-1.093875730217014</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.891582553414491</v>
+        <v>-2.846678108907795</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.450407724701313</v>
+        <v>1.477350391405331</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.79029738328709</v>
+        <v>-10.62582501402354</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.14085538327244</v>
+        <v>-1.075066435567019</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.775311716298147</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.483490297873237</v>
+        <v>1.510432964577255</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.52646051608302</v>
+        <v>-10.36198814681947</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.045204117703719</v>
+        <v>-0.9794151699982989</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.775311716298147</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.473606816560329</v>
+        <v>1.500549483264347</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25921871521462</v>
+        <v>-10.09474634595107</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9401419578557335</v>
+        <v>-0.8743530101503141</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.775311716298147</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.471772256060956</v>
+        <v>1.498714922764973</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.16131167653813</v>
+        <v>-9.996839307274579</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9012794573585983</v>
+        <v>-0.8354905096531784</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.752230410944287</v>
+        <v>-2.70732596643759</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.512263391003829</v>
+        <v>1.539206057707846</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13735813556217</v>
+        <v>-9.972885766298621</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8910295348227213</v>
+        <v>-0.8252405871173019</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.728276869968329</v>
+        <v>-2.683372425461633</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.527304021734897</v>
+        <v>1.554246688438915</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.873298197239373</v>
+        <v>-9.708825827975824</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7986658756553551</v>
+        <v>-0.7328769279499352</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.464216931645533</v>
+        <v>-2.419312487138837</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.672479668566822</v>
+        <v>1.69942233527084</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.166218573734536</v>
+        <v>-9.001746204470987</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5186210599137207</v>
+        <v>-0.4528321122083012</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.464216931645533</v>
+        <v>-2.419312487138837</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.669692634906521</v>
+        <v>1.696635301610539</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.126034275368346</v>
+        <v>-8.961561906104796</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5022037166794031</v>
+        <v>-0.4364147689739837</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.424032633279342</v>
+        <v>-2.379128188772646</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.694146837814077</v>
+        <v>1.721089504518095</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.045964479830541</v>
+        <v>-8.881492110566992</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4708089772435247</v>
+        <v>-0.4050200295381048</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.343962837741538</v>
+        <v>-2.299058393234842</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.741555536357517</v>
+        <v>1.768498203061534</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.812483257600942</v>
+        <v>-8.648010888337392</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3694920595138322</v>
+        <v>-0.3037031118084128</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.11048161551194</v>
+        <v>-2.065577171005244</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.889568698533128</v>
+        <v>1.916511365237146</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.662816866593428</v>
+        <v>-8.498344497329878</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.312517713423786</v>
+        <v>-0.2467287657183661</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.017578124269404</v>
+        <v>-1.972673679762708</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.942418582965691</v>
+        <v>1.969361249669708</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.53054139296254</v>
+        <v>-8.366069023698991</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.264240037224404</v>
+        <v>-0.1984510895189842</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.885302650638517</v>
+        <v>-1.840398206131821</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.01715135389125</v>
+        <v>2.044094020595267</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.339941718289387</v>
+        <v>-8.175469349025837</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1851851066675057</v>
+        <v>-0.1193961589620862</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.694702975965364</v>
+        <v>-1.649798531458668</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.134326219382778</v>
+        <v>2.161268886086796</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.090941919605806</v>
+        <v>-7.926469550342256</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.07267884597041485</v>
+        <v>-0.006889898264994976</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.694702975965364</v>
+        <v>-1.649798531458668</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.147232560606437</v>
+        <v>2.174175227310454</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.19653190937891</v>
+        <v>-8.032059540115361</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2428907714788751</v>
+        <v>-0.1771018237734552</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.800292965738468</v>
+        <v>-1.755388521231772</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.955902637143356</v>
+        <v>1.982845303847373</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.215266811497507</v>
+        <v>-8.050794442233958</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2018403904492274</v>
+        <v>-0.136051442743808</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.800292965738468</v>
+        <v>-1.755388521231772</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.004446979020442</v>
+        <v>2.03138964572446</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.067326770089908</v>
+        <v>-7.902854400826358</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2625432965743553</v>
+        <v>-0.1967543488689358</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.779972049829911</v>
+        <v>-1.735067605323215</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.896760605877409</v>
+        <v>1.923703272581426</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.043098133700935</v>
+        <v>-7.878625764437386</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2615658282722446</v>
+        <v>-0.1957768805668247</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.710838968934242</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.902583801457314</v>
+        <v>1.929526468161332</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.999549726930245</v>
+        <v>-7.835077357666695</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2511070776590616</v>
+        <v>-0.1853181299536417</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.710838968934242</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.895623189362221</v>
+        <v>1.922565856066239</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.757401333476387</v>
+        <v>-7.592928964212837</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1397853658963752</v>
+        <v>-0.07399641819095537</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.710838968934242</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.910085543743364</v>
+        <v>1.937028210447382</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.694171961708038</v>
+        <v>-7.529699592444489</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1199614967298408</v>
+        <v>-0.05417254902442092</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.710838968934242</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.904617664202559</v>
+        <v>1.931560330906577</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.570880826890908</v>
+        <v>-7.406408457627358</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.07314694879241168</v>
+        <v>-0.007358001086991806</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.632452278623808</v>
+        <v>-1.587547834117112</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.976090439103414</v>
+        <v>2.003033105807432</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.549731627987464</v>
+        <v>-7.385259258723915</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.05698629099370933</v>
+        <v>0.008802656711710544</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.611303079720365</v>
+        <v>-1.566398635213669</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.996480936682805</v>
+        <v>2.023423603386823</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.30596618600402</v>
+        <v>-7.14149381674047</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.03630059414671916</v>
+        <v>0.102089541852139</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.611303079720365</v>
+        <v>-1.566398635213669</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.992261645029856</v>
+        <v>2.019204311733874</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.04193811881076</v>
+        <v>-6.877465749547211</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1440361349440389</v>
+        <v>0.2098250826494588</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.409437680904411</v>
+        <v>-1.364533236397715</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.115505198239444</v>
+        <v>2.142447864943462</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.792087724861686</v>
+        <v>-6.627615355598136</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.236718367507371</v>
+        <v>0.3025073152127908</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.409437680904411</v>
+        <v>-1.364533236397715</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.108247273223146</v>
+        <v>2.135189939927164</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.616195632394254</v>
+        <v>-6.451723263130704</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3106743280149926</v>
+        <v>0.3764632757204125</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.409437680904411</v>
+        <v>-1.364533236397715</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.111846396743795</v>
+        <v>2.138789063447812</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.44474916937179</v>
+        <v>-6.280276800108241</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3925804192785316</v>
+        <v>0.4583693669839515</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.237991217881948</v>
+        <v>-1.193086773375252</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.228041780611826</v>
+        <v>2.254984447315844</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.219716169702967</v>
+        <v>-6.055243800439418</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4816140967623577</v>
+        <v>0.5474030444677775</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.012958218213125</v>
+        <v>-0.9680537737064291</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.362082058029417</v>
+        <v>2.389024724733435</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.00508179206656</v>
+        <v>-5.840609422803011</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5721626488712381</v>
+        <v>0.6379515965766576</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7983238405767183</v>
+        <v>-0.7534193960700223</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.495557485665579</v>
+        <v>2.522500152369596</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.912081750860662</v>
+        <v>-5.747609381597113</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5905569241373927</v>
+        <v>0.6563458718428126</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7983238405767183</v>
+        <v>-0.7534193960700223</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.476751744449374</v>
+        <v>2.503694411153392</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.671651254055802</v>
+        <v>-5.507178884792252</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6884721994842145</v>
+        <v>0.7542611471896343</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5578933437718581</v>
+        <v>-0.512988899265162</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.622753119157168</v>
+        <v>2.649695785861185</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.599408685884607</v>
+        <v>-5.434936316621058</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7212985405875125</v>
+        <v>0.7870874882929324</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5578933437718581</v>
+        <v>-0.512988899265162</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.626682432991988</v>
+        <v>2.653625099696006</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.483468836259422</v>
+        <v>-5.318996466995872</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7683530643549266</v>
+        <v>0.8341420120603464</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4810716127557342</v>
+        <v>-0.4361671682490381</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.673454055519002</v>
+        <v>2.70039672222302</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.240813247836259</v>
+        <v>-5.07634087857271</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8624133709441852</v>
+        <v>0.9282023186496051</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4810716127557342</v>
+        <v>-0.4361671682490381</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.670452126738996</v>
+        <v>2.697394793443014</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.020792449799249</v>
+        <v>-4.856320080535699</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9520007271696036</v>
+        <v>1.017789674875023</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3398517676877539</v>
+        <v>-0.2949473231810579</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.756763070790398</v>
+        <v>2.783705737494416</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.887924760735971</v>
+        <v>-4.723452391472422</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.021041985596738</v>
+        <v>1.086830933302158</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3398517676877539</v>
+        <v>-0.2949473231810579</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.772657253592222</v>
+        <v>2.799599920296239</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.728409657216601</v>
+        <v>-4.563937287953052</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.085993871444788</v>
+        <v>1.151782819150208</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.180336664168384</v>
+        <v>-0.1354322196616879</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.869512160144145</v>
+        <v>2.896454826848163</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.583737512116864</v>
+        <v>-4.419265142853314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.153950832046122</v>
+        <v>1.219739779751542</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.03566451906864659</v>
+        <v>0.009239925438049468</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.966403549765428</v>
+        <v>2.993346216469445</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.643612339474556</v>
+        <v>-4.479139970211007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.116038392504471</v>
+        <v>1.181827340209891</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.09553934642633871</v>
+        <v>-0.05063490191964265</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.916516144752238</v>
+        <v>2.943458811456256</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.556812841695548</v>
+        <v>-4.392340472431998</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.173158684938641</v>
+        <v>1.238947632644061</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.09553934642633871</v>
+        <v>-0.05063490191964265</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.938916638074804</v>
+        <v>2.965859304778822</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.559282548157354</v>
+        <v>-4.394810178893804</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.17224320372733</v>
+        <v>1.23803215143275</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.09800905288814488</v>
+        <v>-0.05310460838144881</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.937507215571133</v>
+        <v>2.96444988227515</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.627652734481364</v>
+        <v>-4.463180365217815</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.155902051672429</v>
+        <v>1.221690999377848</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.08873335385192993</v>
+        <v>-0.04382890934523387</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.954079557467564</v>
+        <v>2.981022224171581</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.506236304854887</v>
+        <v>-4.341763935591338</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.19490533215491</v>
+        <v>1.26069427986033</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.08873335385192993</v>
+        <v>-0.04382890934523387</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.944516266099455</v>
+        <v>2.971458932803472</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.537229464183593</v>
+        <v>-4.372757094920043</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.007217633463815</v>
+        <v>1.073006581169235</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.08873335385192993</v>
+        <v>-0.04382890934523387</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.769225831139842</v>
+        <v>2.796168497843859</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.361755204391123</v>
+        <v>-4.197282835127574</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.081974569372591</v>
+        <v>1.14776351707801</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.08873335385192993</v>
+        <v>-0.04382890934523387</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.77379306313163</v>
+        <v>2.800735729835647</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.472691457032372</v>
+        <v>-4.308219087768823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.013342097077298</v>
+        <v>1.079131044782718</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.08873335385192993</v>
+        <v>-0.04382890934523387</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.749535091892837</v>
+        <v>2.776477758596854</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.675718034575605</v>
+        <v>-4.511245665312056</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9352628512799104</v>
+        <v>1.00105179898533</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2917599313951633</v>
+        <v>-0.2468554868884673</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.630850530586802</v>
+        <v>2.65779319729082</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.517792435640312</v>
+        <v>-4.353320066376763</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.00860547728616</v>
+        <v>1.07439442499158</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2917599313951633</v>
+        <v>-0.2468554868884673</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.641022917018935</v>
+        <v>2.667965583722952</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.431548972613935</v>
+        <v>-4.267076603350385</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.038049133070571</v>
+        <v>1.103838080775991</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2917599313951633</v>
+        <v>-0.2468554868884673</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.635969187592795</v>
+        <v>2.662911854296813</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.432732057264996</v>
+        <v>-4.268259688001447</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.029351674654672</v>
+        <v>1.095140622360092</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2974029798616749</v>
+        <v>-0.2524985353549788</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.624359133957413</v>
+        <v>2.651301800661431</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.309604350270913</v>
+        <v>-4.145131981007363</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.079154630485407</v>
+        <v>1.144943578190827</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2974029798616749</v>
+        <v>-0.2524985353549788</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.624911006990515</v>
+        <v>2.651853673694533</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.216793868820053</v>
+        <v>-4.052321499556504</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.045551514957117</v>
+        <v>1.111340462662536</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2045924984108155</v>
+        <v>-0.1596880539041194</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.609869987752396</v>
+        <v>2.636812654456414</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.168230816599023</v>
+        <v>-4.003758447335473</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.06685021177013</v>
+        <v>1.132639159475549</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1560294461897853</v>
+        <v>-0.1111250016830893</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.640881295009615</v>
+        <v>2.667823961713633</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.055559598362773</v>
+        <v>-3.891087229099223</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.106994407576352</v>
+        <v>1.172783355281773</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.04335822795353511</v>
+        <v>0.001546216553160951</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.703559734463088</v>
+        <v>2.730502401167106</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.943182597180101</v>
+        <v>-3.77871022791655</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.157436503880089</v>
+        <v>1.223225451585509</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.04335822795353511</v>
+        <v>0.001546216553160951</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.709051030293756</v>
+        <v>2.735993696997773</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.141417166066831</v>
+        <v>-3.976944796803281</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.089639878093936</v>
+        <v>1.155428825799356</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2415927968402657</v>
+        <v>-0.1966883523335696</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.601607490730256</v>
+        <v>2.628550157434274</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.22441844709211</v>
+        <v>-4.05994607782856</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8947950856844775</v>
+        <v>0.9605840333898976</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2601636813674394</v>
+        <v>-0.2152592368607434</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.428820680014605</v>
+        <v>2.455763346718623</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.065224175035533</v>
+        <v>-3.900751805771983</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.078622455226314</v>
+        <v>1.144411402931734</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2601636813674394</v>
+        <v>-0.2152592368607434</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.548970340733811</v>
+        <v>2.575913007437828</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.151822758016636</v>
+        <v>-3.987350388753086</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.058496048136196</v>
+        <v>1.124284995841615</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2601636813674394</v>
+        <v>-0.2152592368607434</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.563483366836134</v>
+        <v>2.590426033540151</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.113439095458485</v>
+        <v>-3.948966726194935</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.071268954501825</v>
+        <v>1.137057902207245</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2217800188092883</v>
+        <v>-0.1768755743025922</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.583933005713393</v>
+        <v>2.610875672417411</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.936322765423319</v>
+        <v>-3.771850396159769</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.138844515361193</v>
+        <v>1.204633463066613</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2217800188092883</v>
+        <v>-0.1768755743025922</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.580662034558695</v>
+        <v>2.607604701262713</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.906620641447025</v>
+        <v>-3.742148272183476</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.151408756713624</v>
+        <v>1.217197704419044</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2262501440246016</v>
+        <v>-0.1813456995179056</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578663351191421</v>
+        <v>2.605606017895438</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.727245220208258</v>
+        <v>-3.562772850944707</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.216945900515545</v>
+        <v>1.282734848220965</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.06947338585388296</v>
+        <v>-0.0245689413471869</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.666516381400266</v>
+        <v>2.693459048104283</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.772259433728864</v>
+        <v>-3.607787064465314</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.179747670438892</v>
+        <v>1.245536618144312</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.09982228116848757</v>
+        <v>-0.05491783666179151</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.629114499543093</v>
+        <v>2.65605716624711</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.039263944001299</v>
+        <v>-3.874791574737749</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.078637428668864</v>
+        <v>1.144426376374284</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2941853192114361</v>
+        <v>-0.2492808747047401</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.518188239056269</v>
+        <v>2.545130905760287</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.328051164460215</v>
+        <v>-4.163578795196664</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9623264623817991</v>
+        <v>1.028115410087219</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3952714393104365</v>
+        <v>-0.3503669948037405</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.456740488893371</v>
+        <v>2.483683155597388</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.552643980021016</v>
+        <v>3.780837767502354</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.294763650564169</v>
+        <v>-4.131103209025892</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.973241429494534</v>
+        <v>1.038705606109845</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3952714393104365</v>
+        <v>-0.3503669948037405</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.454340450447687</v>
+        <v>2.481283117151705</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>133.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.7%</t>
+          <t>-583.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.4%</t>
+          <t>-275.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-1017.5%</t>
+          <t>-123.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-259.0%</t>
+          <t>-256.0%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.9%</t>
+          <t>-196.1%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.13391361967919</v>
+        <v>-10.29838598894274</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9164953362517476</v>
+        <v>-0.982284283957167</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.319584068347235</v>
+        <v>-2.364488512853932</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.745676094925334</v>
+        <v>1.718733428221316</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.35195139131037</v>
+        <v>-10.51642376057391</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9992278904197822</v>
+        <v>-1.065016838125203</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.494354836443134</v>
+        <v>-2.539259280949831</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.645296188552231</v>
+        <v>1.618353521848213</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.27848155964292</v>
+        <v>-10.44295392890647</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.954468256259382</v>
+        <v>-1.020257203964801</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.420885004775686</v>
+        <v>-2.465789449282382</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.704749789046121</v>
+        <v>1.677807122342103</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.45360597702946</v>
+        <v>-10.61807834629301</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.009962802466482</v>
+        <v>-1.075751750171902</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.59600942216223</v>
+        <v>-2.640913866668926</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.614230359361711</v>
+        <v>1.587287692657693</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.68805807104395</v>
+        <v>-10.8525304403075</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.110962804973874</v>
+        <v>-1.176751752679294</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.59600942216223</v>
+        <v>-2.640913866668926</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.607011194460115</v>
+        <v>1.580068527756097</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.97586191558119</v>
+        <v>-11.14033428484474</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.232756533562746</v>
+        <v>-1.298545481268166</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.883813266699468</v>
+        <v>-2.928717711206164</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.427656696963796</v>
+        <v>1.400714030259778</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.20568636274501</v>
+        <v>-11.37015873200856</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.323570522589719</v>
+        <v>-1.38935947029514</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.046460803769628</v>
+        <v>-3.091365248276325</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.331183964560256</v>
+        <v>1.304241297856238</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.43771528248127</v>
+        <v>-11.60218765174482</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.413688361855109</v>
+        <v>-1.47947730956053</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.108473500958052</v>
+        <v>-3.153377945464748</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.296670074876317</v>
+        <v>1.269727408172299</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.38569976851246</v>
+        <v>-11.55017213777601</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.388891820581184</v>
+        <v>-1.454680768286603</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.108473500958052</v>
+        <v>-3.153377945464748</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.300660410562718</v>
+        <v>1.2737177438587</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.52737161023658</v>
+        <v>-11.69184397950013</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.447035784169573</v>
+        <v>-1.512824731874993</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.108473500958052</v>
+        <v>-3.153377945464748</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.299185183663976</v>
+        <v>1.272242516959958</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.47778076581175</v>
+        <v>-11.6422531350753</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.412146036234768</v>
+        <v>-1.477934983940187</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.058882656533218</v>
+        <v>-3.103787101039914</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.343993100483749</v>
+        <v>1.317050433779731</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.27862865857465</v>
+        <v>-11.4431010278382</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.345536326986611</v>
+        <v>-1.41132527469203</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.893560130583404</v>
+        <v>-2.938464575090101</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.430135482406954</v>
+        <v>1.403192815702936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.05278350585524</v>
+        <v>-11.21725587511879</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.245619192862638</v>
+        <v>-1.311408140568058</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.851633454996241</v>
+        <v>-2.896537899502937</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.46487056079546</v>
+        <v>1.437927894091443</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.92820484951765</v>
+        <v>-11.0926772187812</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.194648585771543</v>
+        <v>-1.260437533476962</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.851633454996241</v>
+        <v>-2.896537899502937</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.466009705351519</v>
+        <v>1.439067038647502</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.98110013756193</v>
+        <v>-11.14557250682548</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.213172926827149</v>
+        <v>-1.278961874532569</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.846678108907795</v>
+        <v>-2.891582553414491</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.471616687166695</v>
+        <v>1.444674020462677</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69719140663318</v>
+        <v>-10.86166377589673</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.093875730217014</v>
+        <v>-1.159664677922433</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.846678108907795</v>
+        <v>-2.891582553414491</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.477350391405331</v>
+        <v>1.450407724701313</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62582501402354</v>
+        <v>-10.79029738328709</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.075066435567019</v>
+        <v>-1.14085538327244</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.775311716298147</v>
+        <v>-2.820216160804843</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.510432964577255</v>
+        <v>1.483490297873237</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36198814681947</v>
+        <v>-10.52646051608302</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9794151699982989</v>
+        <v>-1.045204117703719</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.775311716298147</v>
+        <v>-2.820216160804843</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.500549483264347</v>
+        <v>1.473606816560329</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.09474634595107</v>
+        <v>-10.25921871521462</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8743530101503141</v>
+        <v>-0.9401419578557335</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.775311716298147</v>
+        <v>-2.820216160804843</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.498714922764973</v>
+        <v>1.471772256060956</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.996839307274579</v>
+        <v>-10.16131167653813</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8354905096531784</v>
+        <v>-0.9012794573585983</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.70732596643759</v>
+        <v>-2.752230410944287</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.539206057707846</v>
+        <v>1.512263391003829</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.972885766298621</v>
+        <v>-10.13735813556217</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8252405871173019</v>
+        <v>-0.8910295348227213</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.683372425461633</v>
+        <v>-2.728276869968329</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.554246688438915</v>
+        <v>1.527304021734897</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.708825827975824</v>
+        <v>-9.873298197239373</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7328769279499352</v>
+        <v>-0.7986658756553551</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.419312487138837</v>
+        <v>-2.464216931645533</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.69942233527084</v>
+        <v>1.672479668566822</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.001746204470987</v>
+        <v>-9.166218573734536</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4528321122083012</v>
+        <v>-0.5186210599137207</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.419312487138837</v>
+        <v>-2.464216931645533</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.696635301610539</v>
+        <v>1.669692634906521</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.961561906104796</v>
+        <v>-9.126034275368346</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4364147689739837</v>
+        <v>-0.5022037166794031</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.379128188772646</v>
+        <v>-2.424032633279342</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.721089504518095</v>
+        <v>1.694146837814077</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.881492110566992</v>
+        <v>-9.045964479830541</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4050200295381048</v>
+        <v>-0.4708089772435247</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.299058393234842</v>
+        <v>-2.343962837741538</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.768498203061534</v>
+        <v>1.741555536357517</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.648010888337392</v>
+        <v>-8.812483257600942</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3037031118084128</v>
+        <v>-0.3694920595138322</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.065577171005244</v>
+        <v>-2.11048161551194</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.916511365237146</v>
+        <v>1.889568698533128</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.498344497329878</v>
+        <v>-8.662816866593428</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2467287657183661</v>
+        <v>-0.312517713423786</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.972673679762708</v>
+        <v>-2.017578124269404</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.969361249669708</v>
+        <v>1.942418582965691</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.366069023698991</v>
+        <v>-8.53054139296254</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1984510895189842</v>
+        <v>-0.264240037224404</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.840398206131821</v>
+        <v>-1.885302650638517</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.044094020595267</v>
+        <v>2.01715135389125</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.175469349025837</v>
+        <v>-8.339941718289387</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1193961589620862</v>
+        <v>-0.1851851066675057</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.649798531458668</v>
+        <v>-1.694702975965364</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.161268886086796</v>
+        <v>2.134326219382778</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.926469550342256</v>
+        <v>-8.090941919605806</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.006889898264994976</v>
+        <v>-0.07267884597041485</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.649798531458668</v>
+        <v>-1.694702975965364</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.174175227310454</v>
+        <v>2.147232560606437</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.032059540115361</v>
+        <v>-8.19653190937891</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1771018237734552</v>
+        <v>-0.2428907714788751</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.755388521231772</v>
+        <v>-1.800292965738468</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.982845303847373</v>
+        <v>1.955902637143356</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.050794442233958</v>
+        <v>-8.215266811497507</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.136051442743808</v>
+        <v>-0.2018403904492274</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.755388521231772</v>
+        <v>-1.800292965738468</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.03138964572446</v>
+        <v>2.004446979020442</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.902854400826358</v>
+        <v>-8.067326770089908</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1967543488689358</v>
+        <v>-0.2625432965743553</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.735067605323215</v>
+        <v>-1.779972049829911</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.923703272581426</v>
+        <v>1.896760605877409</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.878625764437386</v>
+        <v>-7.967716715765349</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1957768805668247</v>
+        <v>-0.2314132610980102</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.710838968934242</v>
+        <v>-1.680361995505352</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.929526468161332</v>
+        <v>1.947812652218666</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.835077357666695</v>
+        <v>-7.924168308994659</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1853181299536417</v>
+        <v>-0.2209545104848272</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.710838968934242</v>
+        <v>-1.680361995505352</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.922565856066239</v>
+        <v>1.940852040123572</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.592928964212837</v>
+        <v>-7.682019915540801</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.07399641819095537</v>
+        <v>-0.1096327987221408</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.710838968934242</v>
+        <v>-1.680361995505352</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.937028210447382</v>
+        <v>1.955314394504716</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.529699592444489</v>
+        <v>-7.618790543772453</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.05417254902442092</v>
+        <v>-0.08980892955560638</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.710838968934242</v>
+        <v>-1.680361995505352</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.931560330906577</v>
+        <v>1.949846514963911</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.406408457627358</v>
+        <v>-7.495499408955322</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.007358001086991806</v>
+        <v>-0.04299438161817726</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.587547834117112</v>
+        <v>-1.557070860688222</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.003033105807432</v>
+        <v>2.021319289864766</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.385259258723915</v>
+        <v>-7.474350210051878</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.008802656711710544</v>
+        <v>-0.02683372381947491</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.566398635213669</v>
+        <v>-1.535921661784779</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.023423603386823</v>
+        <v>2.041709787444157</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.14149381674047</v>
+        <v>-7.230584768068434</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.102089541852139</v>
+        <v>0.06645316132095358</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.566398635213669</v>
+        <v>-1.535921661784779</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.019204311733874</v>
+        <v>2.037490495791208</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.877465749547211</v>
+        <v>-6.966556700875174</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2098250826494588</v>
+        <v>0.1741887021182738</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.364533236397715</v>
+        <v>-1.334056262968825</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.142447864943462</v>
+        <v>2.160734049000796</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.627615355598136</v>
+        <v>-6.716706306926099</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3025073152127908</v>
+        <v>0.2668709346816058</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.364533236397715</v>
+        <v>-1.334056262968825</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.135189939927164</v>
+        <v>2.153476123984498</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.451723263130704</v>
+        <v>-6.540814214458667</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3764632757204125</v>
+        <v>0.3408268951892275</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.364533236397715</v>
+        <v>-1.334056262968825</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.138789063447812</v>
+        <v>2.157075247505147</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.280276800108241</v>
+        <v>-6.369367751436203</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4583693669839515</v>
+        <v>0.4227329864527665</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.193086773375252</v>
+        <v>-1.162609799946362</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.254984447315844</v>
+        <v>2.273270631373178</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.055243800439418</v>
+        <v>-6.144334751767381</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5474030444677775</v>
+        <v>0.5117666639365925</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9680537737064291</v>
+        <v>-0.937576800277539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.389024724733435</v>
+        <v>2.407310908790769</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.840609422803011</v>
+        <v>-5.929700374130974</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6379515965766576</v>
+        <v>0.6023152160454726</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7534193960700223</v>
+        <v>-0.7229424226411322</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.522500152369596</v>
+        <v>2.540786336426931</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.747609381597113</v>
+        <v>-5.836700332925076</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6563458718428126</v>
+        <v>0.6207094913116276</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7534193960700223</v>
+        <v>-0.7229424226411322</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.503694411153392</v>
+        <v>2.521980595210726</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.507178884792252</v>
+        <v>-5.596269836120215</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7542611471896343</v>
+        <v>0.7186247666584489</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.512988899265162</v>
+        <v>-0.4825119258362719</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.649695785861185</v>
+        <v>2.667981969918519</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.434936316621058</v>
+        <v>-5.524027267949021</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7870874882929324</v>
+        <v>0.751451107761747</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.512988899265162</v>
+        <v>-0.4825119258362719</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.653625099696006</v>
+        <v>2.67191128375334</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.318996466995872</v>
+        <v>-5.408087418323835</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8341420120603464</v>
+        <v>0.7985056315291614</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4361671682490381</v>
+        <v>-0.405690194820148</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.70039672222302</v>
+        <v>2.718682906280354</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.07634087857271</v>
+        <v>-5.165431829900673</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9282023186496051</v>
+        <v>0.8925659381184197</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4361671682490381</v>
+        <v>-0.405690194820148</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.697394793443014</v>
+        <v>2.715680977500348</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.856320080535699</v>
+        <v>-4.945411031863662</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.017789674875023</v>
+        <v>0.9821532943438382</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2949473231810579</v>
+        <v>-0.2644703497521678</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.783705737494416</v>
+        <v>2.80199192155175</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.723452391472422</v>
+        <v>-4.812543342800384</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.086830933302158</v>
+        <v>1.051194552770973</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2949473231810579</v>
+        <v>-0.2644703497521678</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.799599920296239</v>
+        <v>2.817886104353573</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.563937287953052</v>
+        <v>-4.653028239281014</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.151782819150208</v>
+        <v>1.116146438619022</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1354322196616879</v>
+        <v>-0.1049552462327978</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.896454826848163</v>
+        <v>2.914741010905497</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.419265142853314</v>
+        <v>-4.508356094181277</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.219739779751542</v>
+        <v>1.184103399220357</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.009239925438049468</v>
+        <v>0.03971689886693958</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.993346216469445</v>
+        <v>3.011632400526779</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.479139970211007</v>
+        <v>-4.568230921538969</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.181827340209891</v>
+        <v>1.146190959678706</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.05063490191964265</v>
+        <v>-0.02015792849075254</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.943458811456256</v>
+        <v>2.96174499551359</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.392340472431998</v>
+        <v>-4.481431423759961</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.238947632644061</v>
+        <v>1.203311252112875</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.05063490191964265</v>
+        <v>-0.02015792849075254</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.965859304778822</v>
+        <v>2.984145488836156</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.394810178893804</v>
+        <v>-4.483901130221767</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.23803215143275</v>
+        <v>1.202395770901565</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.05310460838144881</v>
+        <v>-0.02262763495255871</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.96444988227515</v>
+        <v>2.982736066332484</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.463180365217815</v>
+        <v>-4.552271316545777</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.221690999377848</v>
+        <v>1.186054618846663</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.04382890934523387</v>
+        <v>-0.01335193591634376</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.981022224171581</v>
+        <v>2.999308408228915</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.341763935591338</v>
+        <v>-4.430854886919301</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.26069427986033</v>
+        <v>1.225057899329145</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.04382890934523387</v>
+        <v>-0.01335193591634376</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.971458932803472</v>
+        <v>2.989745116860806</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.372757094920043</v>
+        <v>-4.461848046248006</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.073006581169235</v>
+        <v>1.03737020063805</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.04382890934523387</v>
+        <v>-0.01335193591634376</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.796168497843859</v>
+        <v>2.814454681901193</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.197282835127574</v>
+        <v>-4.286373786455536</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.14776351707801</v>
+        <v>1.112127136546825</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.04382890934523387</v>
+        <v>-0.01335193591634376</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.800735729835647</v>
+        <v>2.819021913892981</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.308219087768823</v>
+        <v>-4.397310039096785</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.079131044782718</v>
+        <v>1.043494664251533</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.04382890934523387</v>
+        <v>-0.01335193591634376</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.776477758596854</v>
+        <v>2.794763942654188</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.511245665312056</v>
+        <v>-4.600336616640019</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.00105179898533</v>
+        <v>0.9654154184541452</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2468554868884673</v>
+        <v>-0.2163785134595771</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.65779319729082</v>
+        <v>2.676079381348154</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.353320066376763</v>
+        <v>-4.442411017704726</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.07439442499158</v>
+        <v>1.038758044460395</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2468554868884673</v>
+        <v>-0.2163785134595771</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.667965583722952</v>
+        <v>2.686251767780286</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.267076603350385</v>
+        <v>-4.356167554678348</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.103838080775991</v>
+        <v>1.068201700244806</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2468554868884673</v>
+        <v>-0.2163785134595771</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.662911854296813</v>
+        <v>2.681198038354147</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.268259688001447</v>
+        <v>-4.357350639329409</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.095140622360092</v>
+        <v>1.059504241828907</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2524985353549788</v>
+        <v>-0.2220215619260887</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.651301800661431</v>
+        <v>2.669587984718765</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.145131981007363</v>
+        <v>-4.234222932335326</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.144943578190827</v>
+        <v>1.109307197659642</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2524985353549788</v>
+        <v>-0.2220215619260887</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.651853673694533</v>
+        <v>2.670139857751867</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.052321499556504</v>
+        <v>-4.141412450884467</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.111340462662536</v>
+        <v>1.075704082131351</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1596880539041194</v>
+        <v>-0.1292110804752293</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.636812654456414</v>
+        <v>2.655098838513748</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.003758447335473</v>
+        <v>-4.092849398663437</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132639159475549</v>
+        <v>1.097002778944364</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1111250016830893</v>
+        <v>-0.08064802825419914</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.667823961713633</v>
+        <v>2.686110145770967</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.891087229099223</v>
+        <v>-3.980178180427187</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172783355281773</v>
+        <v>1.137146974750587</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.001546216553160951</v>
+        <v>0.03202318998205106</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.730502401167106</v>
+        <v>2.74878858522444</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.77871022791655</v>
+        <v>-3.867801179244514</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.223225451585509</v>
+        <v>1.187589071054324</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.001546216553160951</v>
+        <v>0.03202318998205106</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.735993696997773</v>
+        <v>2.754279881055107</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.976944796803281</v>
+        <v>-4.066035748131244</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.155428825799356</v>
+        <v>1.11979244526817</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1966883523335696</v>
+        <v>-0.1662113789046795</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.628550157434274</v>
+        <v>2.646836341491608</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.05994607782856</v>
+        <v>-4.149037029156523</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9605840333898976</v>
+        <v>0.9249476528587122</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2152592368607434</v>
+        <v>-0.1847822634318533</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.455763346718623</v>
+        <v>2.474049530775957</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.900751805771983</v>
+        <v>-3.989842757099947</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.144411402931734</v>
+        <v>1.108775022400548</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2152592368607434</v>
+        <v>-0.1847822634318533</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.575913007437828</v>
+        <v>2.594199191495163</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.987350388753086</v>
+        <v>-4.07644134008105</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.124284995841615</v>
+        <v>1.08864861531043</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2152592368607434</v>
+        <v>-0.1847822634318533</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.590426033540151</v>
+        <v>2.608712217597486</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.948966726194935</v>
+        <v>-4.038057677522899</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.137057902207245</v>
+        <v>1.101421521676059</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1768755743025922</v>
+        <v>-0.1463986008737021</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.610875672417411</v>
+        <v>2.629161856474745</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.771850396159769</v>
+        <v>-3.860941347487733</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.204633463066613</v>
+        <v>1.168997082535427</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1768755743025922</v>
+        <v>-0.1463986008737021</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.607604701262713</v>
+        <v>2.625890885320047</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.742148272183476</v>
+        <v>-3.83123922351144</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.217197704419044</v>
+        <v>1.181561323887858</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1813456995179056</v>
+        <v>-0.1508687260890155</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.605606017895438</v>
+        <v>2.623892201952772</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.562772850944707</v>
+        <v>-3.651863802272672</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282734848220965</v>
+        <v>1.247098467689779</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.0245689413471869</v>
+        <v>0.005908032081703207</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.693459048104283</v>
+        <v>2.711745232161618</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.607787064465314</v>
+        <v>-3.696878015793278</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245536618144312</v>
+        <v>1.209900237613127</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.05491783666179151</v>
+        <v>-0.0244408632329014</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.65605716624711</v>
+        <v>2.674343350304444</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.874791574737749</v>
+        <v>-3.963882526065714</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.144426376374284</v>
+        <v>1.108789995843098</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2492808747047401</v>
+        <v>-0.21880390127585</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.545130905760287</v>
+        <v>2.563417089817621</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.163578795196664</v>
+        <v>-4.252669746524629</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.028115410087219</v>
+        <v>0.9924790295560335</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3503669948037405</v>
+        <v>-0.3198900213748503</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.483683155597388</v>
+        <v>2.501969339654722</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.780837767502354</v>
+        <v>3.795866445187176</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.131103209025892</v>
+        <v>-4.220194160353857</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.038705606109845</v>
+        <v>1.003069225578659</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3503669948037405</v>
+        <v>-0.3198900213748503</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.481283117151705</v>
+        <v>2.499569301209039</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.5%</t>
+          <t>-46.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.0%</t>
+          <t>441.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.6%</t>
+          <t>-594.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-275.9%</t>
+          <t>-280.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.4%</t>
+          <t>-117.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.0%</t>
+          <t>-263.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-196.1%</t>
+          <t>-181.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1961"/>
+  <dimension ref="A1:G1962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.967716715765349</v>
+        <v>-8.043098133700935</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2314132610980102</v>
+        <v>-0.2615658282722446</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.680361995505352</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.947812652218666</v>
+        <v>1.902583801457314</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.924168308994659</v>
+        <v>-7.999549726930245</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2209545104848272</v>
+        <v>-0.2511070776590616</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.680361995505352</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.940852040123572</v>
+        <v>1.895623189362221</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.682019915540801</v>
+        <v>-7.757401333476387</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1096327987221408</v>
+        <v>-0.1397853658963752</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.680361995505352</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.955314394504716</v>
+        <v>1.910085543743364</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.618790543772453</v>
+        <v>-7.694171961708038</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08980892955560638</v>
+        <v>-0.1199614967298408</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.680361995505352</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.949846514963911</v>
+        <v>1.904617664202559</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.495499408955322</v>
+        <v>-7.570880826890908</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04299438161817726</v>
+        <v>-0.07314694879241168</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.557070860688222</v>
+        <v>-1.632452278623808</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.021319289864766</v>
+        <v>1.976090439103414</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.474350210051878</v>
+        <v>-7.549731627987464</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02683372381947491</v>
+        <v>-0.05698629099370933</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.535921661784779</v>
+        <v>-1.611303079720365</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.041709787444157</v>
+        <v>1.996480936682805</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.230584768068434</v>
+        <v>-7.30596618600402</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06645316132095358</v>
+        <v>0.03630059414671916</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.535921661784779</v>
+        <v>-1.611303079720365</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.037490495791208</v>
+        <v>1.992261645029856</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.966556700875174</v>
+        <v>-7.04193811881076</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1741887021182738</v>
+        <v>0.1440361349440389</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.334056262968825</v>
+        <v>-1.409437680904411</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.160734049000796</v>
+        <v>2.115505198239444</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.716706306926099</v>
+        <v>-6.792087724861686</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2668709346816058</v>
+        <v>0.236718367507371</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.334056262968825</v>
+        <v>-1.409437680904411</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.153476123984498</v>
+        <v>2.108247273223146</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.540814214458667</v>
+        <v>-6.616195632394254</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3408268951892275</v>
+        <v>0.3106743280149926</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.334056262968825</v>
+        <v>-1.409437680904411</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.157075247505147</v>
+        <v>2.111846396743795</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.369367751436203</v>
+        <v>-6.44474916937179</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4227329864527665</v>
+        <v>0.3925804192785316</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.162609799946362</v>
+        <v>-1.237991217881948</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.273270631373178</v>
+        <v>2.228041780611826</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.144334751767381</v>
+        <v>-6.219716169702967</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5117666639365925</v>
+        <v>0.4816140967623577</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.937576800277539</v>
+        <v>-1.012958218213125</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.407310908790769</v>
+        <v>2.362082058029417</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.929700374130974</v>
+        <v>-6.00508179206656</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6023152160454726</v>
+        <v>0.5721626488712381</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7229424226411322</v>
+        <v>-0.7983238405767183</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.540786336426931</v>
+        <v>2.495557485665579</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.836700332925076</v>
+        <v>-5.912081750860662</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6207094913116276</v>
+        <v>0.5905569241373927</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7229424226411322</v>
+        <v>-0.7983238405767183</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.521980595210726</v>
+        <v>2.476751744449374</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.596269836120215</v>
+        <v>-5.671651254055802</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7186247666584489</v>
+        <v>0.6884721994842145</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4825119258362719</v>
+        <v>-0.5578933437718581</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.667981969918519</v>
+        <v>2.622753119157168</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.524027267949021</v>
+        <v>-5.599408685884607</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.751451107761747</v>
+        <v>0.7212985405875125</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4825119258362719</v>
+        <v>-0.5578933437718581</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.67191128375334</v>
+        <v>2.626682432991988</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.408087418323835</v>
+        <v>-5.483468836259422</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7985056315291614</v>
+        <v>0.7683530643549266</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.405690194820148</v>
+        <v>-0.4810716127557342</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.718682906280354</v>
+        <v>2.673454055519002</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.165431829900673</v>
+        <v>-5.240813247836259</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8925659381184197</v>
+        <v>0.8624133709441852</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.405690194820148</v>
+        <v>-0.4810716127557342</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.715680977500348</v>
+        <v>2.670452126738996</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.945411031863662</v>
+        <v>-5.020792449799249</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9821532943438382</v>
+        <v>0.9520007271696036</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2644703497521678</v>
+        <v>-0.3398517676877539</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.80199192155175</v>
+        <v>2.756763070790398</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.812543342800384</v>
+        <v>-4.887924760735971</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.051194552770973</v>
+        <v>1.021041985596738</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2644703497521678</v>
+        <v>-0.3398517676877539</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.817886104353573</v>
+        <v>2.772657253592222</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.653028239281014</v>
+        <v>-4.728409657216601</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.116146438619022</v>
+        <v>1.085993871444788</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1049552462327978</v>
+        <v>-0.180336664168384</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.914741010905497</v>
+        <v>2.869512160144145</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.508356094181277</v>
+        <v>-4.583737512116864</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.184103399220357</v>
+        <v>1.153950832046122</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.03971689886693958</v>
+        <v>-0.03566451906864659</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.011632400526779</v>
+        <v>2.966403549765428</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.568230921538969</v>
+        <v>-4.643612339474556</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.146190959678706</v>
+        <v>1.116038392504471</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.02015792849075254</v>
+        <v>-0.09553934642633871</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.96174499551359</v>
+        <v>2.916516144752238</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.481431423759961</v>
+        <v>-4.556812841695548</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.203311252112875</v>
+        <v>1.173158684938641</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.02015792849075254</v>
+        <v>-0.09553934642633871</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.984145488836156</v>
+        <v>2.938916638074804</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.483901130221767</v>
+        <v>-4.559282548157354</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.202395770901565</v>
+        <v>1.17224320372733</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.02262763495255871</v>
+        <v>-0.09800905288814488</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.982736066332484</v>
+        <v>2.937507215571133</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.552271316545777</v>
+        <v>-4.627652734481364</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.186054618846663</v>
+        <v>1.155902051672429</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.01335193591634376</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.999308408228915</v>
+        <v>2.954079557467564</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.430854886919301</v>
+        <v>-4.506236304854887</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.225057899329145</v>
+        <v>1.19490533215491</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.01335193591634376</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.989745116860806</v>
+        <v>2.944516266099455</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.461848046248006</v>
+        <v>-4.537229464183593</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.03737020063805</v>
+        <v>1.007217633463815</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.01335193591634376</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.814454681901193</v>
+        <v>2.769225831139842</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.286373786455536</v>
+        <v>-4.361755204391123</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.112127136546825</v>
+        <v>1.081974569372591</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.01335193591634376</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.819021913892981</v>
+        <v>2.77379306313163</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.397310039096785</v>
+        <v>-4.472691457032372</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.043494664251533</v>
+        <v>1.013342097077298</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.01335193591634376</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.794763942654188</v>
+        <v>2.749535091892837</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.600336616640019</v>
+        <v>-4.675718034575605</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9654154184541452</v>
+        <v>0.9352628512799104</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2163785134595771</v>
+        <v>-0.2917599313951633</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.676079381348154</v>
+        <v>2.630850530586802</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.442411017704726</v>
+        <v>-4.517792435640312</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.038758044460395</v>
+        <v>1.00860547728616</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2163785134595771</v>
+        <v>-0.2917599313951633</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.686251767780286</v>
+        <v>2.641022917018935</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.356167554678348</v>
+        <v>-4.431548972613935</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.068201700244806</v>
+        <v>1.038049133070571</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2163785134595771</v>
+        <v>-0.2917599313951633</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.681198038354147</v>
+        <v>2.635969187592795</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.357350639329409</v>
+        <v>-4.432732057264996</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.059504241828907</v>
+        <v>1.029351674654672</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2220215619260887</v>
+        <v>-0.2974029798616749</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.669587984718765</v>
+        <v>2.624359133957413</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.234222932335326</v>
+        <v>-4.309604350270913</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.109307197659642</v>
+        <v>1.079154630485407</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2220215619260887</v>
+        <v>-0.2974029798616749</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.670139857751867</v>
+        <v>2.624911006990515</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279497</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.141412450884467</v>
+        <v>-4.216793868820053</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.075704082131351</v>
+        <v>1.045551514957117</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1292110804752293</v>
+        <v>-0.2045924984108155</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.655098838513748</v>
+        <v>2.609869987752396</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.092849398663437</v>
+        <v>-4.168230816599023</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.097002778944364</v>
+        <v>1.06685021177013</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.08064802825419914</v>
+        <v>-0.1560294461897853</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.686110145770967</v>
+        <v>2.640881295009615</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.980178180427187</v>
+        <v>-4.055559598362773</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.137146974750587</v>
+        <v>1.106994407576352</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.03202318998205106</v>
+        <v>-0.04335822795353511</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.74878858522444</v>
+        <v>2.703559734463088</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.867801179244514</v>
+        <v>-3.943182597180101</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.187589071054324</v>
+        <v>1.157436503880089</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.03202318998205106</v>
+        <v>-0.04335822795353511</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.754279881055107</v>
+        <v>2.709051030293756</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.066035748131244</v>
+        <v>-4.141417166066831</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.11979244526817</v>
+        <v>1.089639878093936</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1662113789046795</v>
+        <v>-0.2415927968402657</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.646836341491608</v>
+        <v>2.601607490730256</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.149037029156523</v>
+        <v>-4.22441844709211</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9249476528587122</v>
+        <v>0.8947950856844775</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1847822634318533</v>
+        <v>-0.2601636813674394</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.474049530775957</v>
+        <v>2.428820680014605</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.989842757099947</v>
+        <v>-4.065224175035533</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.108775022400548</v>
+        <v>1.078622455226314</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1847822634318533</v>
+        <v>-0.2601636813674394</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.594199191495163</v>
+        <v>2.548970340733811</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.07644134008105</v>
+        <v>-4.151822758016636</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.08864861531043</v>
+        <v>1.058496048136196</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1847822634318533</v>
+        <v>-0.2601636813674394</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.608712217597486</v>
+        <v>2.563483366836134</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.038057677522899</v>
+        <v>-4.113439095458485</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.101421521676059</v>
+        <v>1.071268954501825</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1463986008737021</v>
+        <v>-0.2217800188092883</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.629161856474745</v>
+        <v>2.583933005713393</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.860941347487733</v>
+        <v>-3.936322765423319</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.168997082535427</v>
+        <v>1.138844515361193</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1463986008737021</v>
+        <v>-0.2217800188092883</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.625890885320047</v>
+        <v>2.580662034558695</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.83123922351144</v>
+        <v>-3.906620641447025</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.181561323887858</v>
+        <v>1.151408756713624</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1508687260890155</v>
+        <v>-0.2262501440246016</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.623892201952772</v>
+        <v>2.578663351191421</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.651863802272672</v>
+        <v>-3.727245220208258</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.247098467689779</v>
+        <v>1.216945900515545</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.005908032081703207</v>
+        <v>-0.06947338585388296</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.711745232161618</v>
+        <v>2.666516381400266</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.696878015793278</v>
+        <v>-3.772259433728864</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.209900237613127</v>
+        <v>1.179747670438892</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0244408632329014</v>
+        <v>-0.09982228116848757</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.674343350304444</v>
+        <v>2.629114499543093</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.963882526065714</v>
+        <v>-4.039263944001299</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.108789995843098</v>
+        <v>1.078637428668864</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.21880390127585</v>
+        <v>-0.2941853192114361</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.563417089817621</v>
+        <v>2.518188239056269</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.252669746524629</v>
+        <v>-4.328051164460215</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9924790295560335</v>
+        <v>0.9623264623817991</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3198900213748503</v>
+        <v>-0.3952714393104365</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.501969339654722</v>
+        <v>2.456740488893371</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,45 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.795866445187176</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.220194160353857</v>
+        <v>-4.327727766413576</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.003069225578659</v>
+        <v>0.9600557831547711</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3198900213748503</v>
+        <v>-0.3952714393104365</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.499569301209039</v>
+        <v>2.454340450447687</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="2" t="n">
+        <v>45424</v>
+      </c>
+      <c r="B1962" t="n">
+        <v>3.553141227993454</v>
+      </c>
+      <c r="C1962" t="n">
+        <v>2.652076628436173</v>
+      </c>
+      <c r="D1962" t="n">
+        <v>-4.327727766413576</v>
+      </c>
+      <c r="E1962" t="n">
+        <v>0.9600557831547711</v>
+      </c>
+      <c r="F1962" t="n">
+        <v>-0.3952714393104365</v>
+      </c>
+      <c r="G1962" t="n">
+        <v>2.64514042542254</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-33.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>132.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.3%</t>
+          <t>445.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.3%</t>
+          <t>-567.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-61.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.2%</t>
+          <t>-269.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-117.1%</t>
+          <t>-242.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-263.5%</t>
+          <t>-251.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.5%</t>
+          <t>-168.9%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612275</v>
+        <v>3.346417924612276</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.29838598894274</v>
+        <v>-10.13391361967919</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.982284283957167</v>
+        <v>-0.9164953362517476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.364488512853932</v>
+        <v>-2.319584068347235</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.718733428221316</v>
+        <v>1.745676094925334</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.51642376057391</v>
+        <v>-10.35195139131037</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.065016838125203</v>
+        <v>-0.9992278904197822</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.539259280949831</v>
+        <v>-2.494354836443134</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.618353521848213</v>
+        <v>1.645296188552231</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.44295392890647</v>
+        <v>-10.27848155964292</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.020257203964801</v>
+        <v>-0.954468256259382</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.465789449282382</v>
+        <v>-2.420885004775686</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.677807122342103</v>
+        <v>1.704749789046121</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.61807834629301</v>
+        <v>-10.45360597702946</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.075751750171902</v>
+        <v>-1.009962802466482</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.640913866668926</v>
+        <v>-2.59600942216223</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.587287692657693</v>
+        <v>1.614230359361711</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.8525304403075</v>
+        <v>-10.68805807104395</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.176751752679294</v>
+        <v>-1.110962804973874</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.640913866668926</v>
+        <v>-2.59600942216223</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.580068527756097</v>
+        <v>1.607011194460115</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.14033428484474</v>
+        <v>-10.97586191558119</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.298545481268166</v>
+        <v>-1.232756533562746</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.928717711206164</v>
+        <v>-2.883813266699468</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.400714030259778</v>
+        <v>1.427656696963796</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.37015873200856</v>
+        <v>-11.20568636274501</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.38935947029514</v>
+        <v>-1.323570522589719</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.091365248276325</v>
+        <v>-3.046460803769628</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.304241297856238</v>
+        <v>1.331183964560256</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.60218765174482</v>
+        <v>-11.43771528248127</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.47947730956053</v>
+        <v>-1.413688361855109</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.153377945464748</v>
+        <v>-3.108473500958052</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.269727408172299</v>
+        <v>1.296670074876317</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.55017213777601</v>
+        <v>-11.38569976851246</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.454680768286603</v>
+        <v>-1.388891820581184</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.153377945464748</v>
+        <v>-3.108473500958052</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.2737177438587</v>
+        <v>1.300660410562718</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.69184397950013</v>
+        <v>-11.52737161023658</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.512824731874993</v>
+        <v>-1.447035784169573</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.153377945464748</v>
+        <v>-3.108473500958052</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.272242516959958</v>
+        <v>1.299185183663976</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.6422531350753</v>
+        <v>-11.47778076581175</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.477934983940187</v>
+        <v>-1.412146036234768</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.103787101039914</v>
+        <v>-3.058882656533218</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.317050433779731</v>
+        <v>1.343993100483749</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.4431010278382</v>
+        <v>-11.27862865857465</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.41132527469203</v>
+        <v>-1.345536326986611</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.938464575090101</v>
+        <v>-2.893560130583404</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.403192815702936</v>
+        <v>1.430135482406954</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.21725587511879</v>
+        <v>-11.05278350585524</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.311408140568058</v>
+        <v>-1.245619192862638</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.896537899502937</v>
+        <v>-2.851633454996241</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.437927894091443</v>
+        <v>1.46487056079546</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.0926772187812</v>
+        <v>-10.92820484951765</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.260437533476962</v>
+        <v>-1.194648585771543</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.896537899502937</v>
+        <v>-2.851633454996241</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.439067038647502</v>
+        <v>1.466009705351519</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.14557250682548</v>
+        <v>-10.98110013756193</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.278961874532569</v>
+        <v>-1.213172926827149</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.891582553414491</v>
+        <v>-2.846678108907795</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.444674020462677</v>
+        <v>1.471616687166695</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.86166377589673</v>
+        <v>-10.69719140663318</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.159664677922433</v>
+        <v>-1.093875730217014</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.891582553414491</v>
+        <v>-2.846678108907795</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.450407724701313</v>
+        <v>1.477350391405331</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.79029738328709</v>
+        <v>-10.62582501402354</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.14085538327244</v>
+        <v>-1.075066435567019</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.775311716298147</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.483490297873237</v>
+        <v>1.510432964577255</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.52646051608302</v>
+        <v>-10.36198814681947</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.045204117703719</v>
+        <v>-0.9794151699982989</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.775311716298147</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.473606816560329</v>
+        <v>1.500549483264347</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25921871521462</v>
+        <v>-10.09474634595107</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9401419578557335</v>
+        <v>-0.8743530101503141</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.820216160804843</v>
+        <v>-2.775311716298147</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.471772256060956</v>
+        <v>1.498714922764973</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.16131167653813</v>
+        <v>-9.996839307274579</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9012794573585983</v>
+        <v>-0.8354905096531784</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.752230410944287</v>
+        <v>-2.70732596643759</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.512263391003829</v>
+        <v>1.539206057707846</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13735813556217</v>
+        <v>-9.972885766298621</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8910295348227213</v>
+        <v>-0.8252405871173019</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.728276869968329</v>
+        <v>-2.683372425461633</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.527304021734897</v>
+        <v>1.554246688438915</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.873298197239373</v>
+        <v>-9.708825827975824</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7986658756553551</v>
+        <v>-0.7328769279499352</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.464216931645533</v>
+        <v>-2.419312487138837</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.672479668566822</v>
+        <v>1.69942233527084</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.166218573734536</v>
+        <v>-9.001746204470987</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5186210599137207</v>
+        <v>-0.4528321122083012</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.464216931645533</v>
+        <v>-2.419312487138837</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.669692634906521</v>
+        <v>1.696635301610539</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.126034275368346</v>
+        <v>-8.961561906104796</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5022037166794031</v>
+        <v>-0.4364147689739837</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.424032633279342</v>
+        <v>-2.379128188772646</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.694146837814077</v>
+        <v>1.721089504518095</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.045964479830541</v>
+        <v>-8.881492110566992</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4708089772435247</v>
+        <v>-0.4050200295381048</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.343962837741538</v>
+        <v>-2.299058393234842</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.741555536357517</v>
+        <v>1.768498203061534</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.812483257600942</v>
+        <v>-8.648010888337392</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3694920595138322</v>
+        <v>-0.3037031118084128</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.11048161551194</v>
+        <v>-2.065577171005244</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.889568698533128</v>
+        <v>1.916511365237146</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.662816866593428</v>
+        <v>-8.498344497329878</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.312517713423786</v>
+        <v>-0.2467287657183661</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.017578124269404</v>
+        <v>-1.972673679762708</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.942418582965691</v>
+        <v>1.969361249669708</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.53054139296254</v>
+        <v>-8.366069023698991</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.264240037224404</v>
+        <v>-0.1984510895189842</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.885302650638517</v>
+        <v>-1.840398206131821</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.01715135389125</v>
+        <v>2.044094020595267</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.339941718289387</v>
+        <v>-8.175469349025837</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1851851066675057</v>
+        <v>-0.1193961589620862</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.694702975965364</v>
+        <v>-1.649798531458668</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.134326219382778</v>
+        <v>2.161268886086796</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.090941919605806</v>
+        <v>-7.926469550342256</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.07267884597041485</v>
+        <v>-0.006889898264994976</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.694702975965364</v>
+        <v>-1.649798531458668</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.147232560606437</v>
+        <v>2.174175227310454</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.19653190937891</v>
+        <v>-8.032059540115361</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2428907714788751</v>
+        <v>-0.1771018237734552</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.800292965738468</v>
+        <v>-1.755388521231772</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.955902637143356</v>
+        <v>1.982845303847373</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.215266811497507</v>
+        <v>-8.050794442233958</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2018403904492274</v>
+        <v>-0.136051442743808</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.800292965738468</v>
+        <v>-1.755388521231772</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.004446979020442</v>
+        <v>2.03138964572446</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.067326770089908</v>
+        <v>-7.902854400826358</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2625432965743553</v>
+        <v>-0.1967543488689358</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.779972049829911</v>
+        <v>-1.735067605323215</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.896760605877409</v>
+        <v>1.923703272581426</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.043098133700935</v>
+        <v>-7.80690736714938</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2615658282722446</v>
+        <v>-0.1670895216516226</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.639120571646236</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.902583801457314</v>
+        <v>1.972557506534136</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.999549726930245</v>
+        <v>-7.76335896037869</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2511070776590616</v>
+        <v>-0.1566307710384396</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.639120571646236</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.895623189362221</v>
+        <v>1.965596894439043</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.757401333476387</v>
+        <v>-7.521210566924831</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1397853658963752</v>
+        <v>-0.04530905927575324</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.639120571646236</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.910085543743364</v>
+        <v>1.980059248820186</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.694171961708038</v>
+        <v>-7.457981195156483</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1199614967298408</v>
+        <v>-0.02548519010921879</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.755743413440939</v>
+        <v>-1.639120571646236</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.904617664202559</v>
+        <v>1.974591369279381</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262046</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.570880826890908</v>
+        <v>-7.334690060339352</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.07314694879241168</v>
+        <v>0.02132935782821033</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.632452278623808</v>
+        <v>-1.515829436829106</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.976090439103414</v>
+        <v>2.046064144180236</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.549731627987464</v>
+        <v>-7.313540861435909</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.05698629099370933</v>
+        <v>0.03749001562691312</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.611303079720365</v>
+        <v>-1.494680237925663</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.996480936682805</v>
+        <v>2.066454641759627</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.30596618600402</v>
+        <v>-7.069775419452465</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.03630059414671916</v>
+        <v>0.1307769007673412</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.611303079720365</v>
+        <v>-1.494680237925663</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.992261645029856</v>
+        <v>2.062235350106677</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.04193811881076</v>
+        <v>-6.805747352259205</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1440361349440389</v>
+        <v>0.2385124415646613</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.409437680904411</v>
+        <v>-1.292814839109709</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.115505198239444</v>
+        <v>2.185478903316266</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.792087724861686</v>
+        <v>-6.555896958310131</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.236718367507371</v>
+        <v>0.331194674127993</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.409437680904411</v>
+        <v>-1.292814839109709</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.108247273223146</v>
+        <v>2.178220978299968</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.616195632394254</v>
+        <v>-6.380004865842698</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3106743280149926</v>
+        <v>0.4051506346356146</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.409437680904411</v>
+        <v>-1.292814839109709</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.111846396743795</v>
+        <v>2.181820101820616</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.44474916937179</v>
+        <v>-6.208558402820235</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3925804192785316</v>
+        <v>0.4870567258991536</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.237991217881948</v>
+        <v>-1.121368376087246</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.228041780611826</v>
+        <v>2.298015485688648</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.219716169702967</v>
+        <v>-5.983525403151412</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4816140967623577</v>
+        <v>0.5760904033829801</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.012958218213125</v>
+        <v>-0.8963353764184229</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.362082058029417</v>
+        <v>2.432055763106239</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.00508179206656</v>
+        <v>-5.768891025515005</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5721626488712381</v>
+        <v>0.6666389554918601</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7983238405767183</v>
+        <v>-0.6817009987820161</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.495557485665579</v>
+        <v>2.5655311907424</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.912081750860662</v>
+        <v>-5.675890984309107</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5905569241373927</v>
+        <v>0.6850332307580151</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7983238405767183</v>
+        <v>-0.6817009987820161</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.476751744449374</v>
+        <v>2.546725449526196</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.671651254055802</v>
+        <v>-5.435460487504247</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6884721994842145</v>
+        <v>0.7829485061048365</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5578933437718581</v>
+        <v>-0.4412705019771558</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.622753119157168</v>
+        <v>2.692726824233989</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.599408685884607</v>
+        <v>-5.363217919333052</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7212985405875125</v>
+        <v>0.8157748472081345</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5578933437718581</v>
+        <v>-0.4412705019771558</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.626682432991988</v>
+        <v>2.69665613806881</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.483468836259422</v>
+        <v>-5.247278069707867</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7683530643549266</v>
+        <v>0.8628293709755486</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4810716127557342</v>
+        <v>-0.3644487709610319</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.673454055519002</v>
+        <v>2.743427760595824</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.240813247836259</v>
+        <v>-5.004622481284704</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8624133709441852</v>
+        <v>0.9568896775648073</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4810716127557342</v>
+        <v>-0.3644487709610319</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.670452126738996</v>
+        <v>2.740425831815817</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.020792449799249</v>
+        <v>-4.784601683247693</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9520007271696036</v>
+        <v>1.046477033790226</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3398517676877539</v>
+        <v>-0.2232289258930517</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.756763070790398</v>
+        <v>2.82673677586722</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.887924760735971</v>
+        <v>-4.651733994184416</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.021041985596738</v>
+        <v>1.11551829221736</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3398517676877539</v>
+        <v>-0.2232289258930517</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.772657253592222</v>
+        <v>2.842630958669043</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.728409657216601</v>
+        <v>-4.492218890665046</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.085993871444788</v>
+        <v>1.18047017806541</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.180336664168384</v>
+        <v>-0.06371382237368173</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.869512160144145</v>
+        <v>2.939485865220967</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.583737512116864</v>
+        <v>-4.347546745565309</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.153950832046122</v>
+        <v>1.248427138666745</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.03566451906864659</v>
+        <v>0.08095832272605569</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.966403549765428</v>
+        <v>3.036377254842249</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.643612339474556</v>
+        <v>-4.407421572923001</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.116038392504471</v>
+        <v>1.210514699125093</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.09553934642633871</v>
+        <v>0.02108349536836357</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.916516144752238</v>
+        <v>2.98648984982906</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.556812841695548</v>
+        <v>-4.320622075143993</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.173158684938641</v>
+        <v>1.267634991559263</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.09553934642633871</v>
+        <v>0.02108349536836357</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.938916638074804</v>
+        <v>3.008890343151626</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.559282548157354</v>
+        <v>-4.323091781605799</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.17224320372733</v>
+        <v>1.266719510347953</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.09800905288814488</v>
+        <v>0.0186137889065574</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.937507215571133</v>
+        <v>3.007480920647954</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.627652734481364</v>
+        <v>-4.391461967929809</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.155902051672429</v>
+        <v>1.250378358293051</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.08873335385192993</v>
+        <v>0.02788948794277235</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.954079557467564</v>
+        <v>3.024053262544385</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.506236304854887</v>
+        <v>-4.270045538303332</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.19490533215491</v>
+        <v>1.289381638775533</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.08873335385192993</v>
+        <v>0.02788948794277235</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.944516266099455</v>
+        <v>3.014489971176276</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.537229464183593</v>
+        <v>-4.301038697632038</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.007217633463815</v>
+        <v>1.101693940084437</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.08873335385192993</v>
+        <v>0.02788948794277235</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.769225831139842</v>
+        <v>2.839199536216663</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.361755204391123</v>
+        <v>-4.125564437839568</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.081974569372591</v>
+        <v>1.176450875993213</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.08873335385192993</v>
+        <v>0.02788948794277235</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.77379306313163</v>
+        <v>2.843766768208451</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.472691457032372</v>
+        <v>-4.236500690480817</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.013342097077298</v>
+        <v>1.10781840369792</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.08873335385192993</v>
+        <v>0.02788948794277235</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.749535091892837</v>
+        <v>2.819508796969658</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.675718034575605</v>
+        <v>-4.43952726802405</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9352628512799104</v>
+        <v>1.029739157900533</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2917599313951633</v>
+        <v>-0.175137089600461</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.630850530586802</v>
+        <v>2.700824235663624</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.517792435640312</v>
+        <v>-4.281601669088757</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.00860547728616</v>
+        <v>1.103081783906782</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2917599313951633</v>
+        <v>-0.175137089600461</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.641022917018935</v>
+        <v>2.710996622095756</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.431548972613935</v>
+        <v>-4.195358206062379</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.038049133070571</v>
+        <v>1.132525439691193</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2917599313951633</v>
+        <v>-0.175137089600461</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.635969187592795</v>
+        <v>2.705942892669616</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.432732057264996</v>
+        <v>-4.196541290713441</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.029351674654672</v>
+        <v>1.123827981275294</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2974029798616749</v>
+        <v>-0.1807801380669726</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.624359133957413</v>
+        <v>2.694332839034235</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.309604350270913</v>
+        <v>-4.073413583719358</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.079154630485407</v>
+        <v>1.173630937106029</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2974029798616749</v>
+        <v>-0.1807801380669726</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.624911006990515</v>
+        <v>2.694884712067336</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.216793868820053</v>
+        <v>-3.980603102268498</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.045551514957117</v>
+        <v>1.140027821577739</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2045924984108155</v>
+        <v>-0.08796965661611322</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.609869987752396</v>
+        <v>2.679843692829218</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.168230816599023</v>
+        <v>-3.932040050047468</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.06685021177013</v>
+        <v>1.161326518390752</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1560294461897853</v>
+        <v>-0.03940660439508303</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.640881295009615</v>
+        <v>2.710855000086437</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.055559598362773</v>
+        <v>-3.819368831811218</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.106994407576352</v>
+        <v>1.201470714196975</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.04335822795353511</v>
+        <v>0.07326461384116717</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.703559734463088</v>
+        <v>2.77353343953991</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.943182597180101</v>
+        <v>-3.706991830628545</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.157436503880089</v>
+        <v>1.251912810500711</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.04335822795353511</v>
+        <v>0.07326461384116717</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.709051030293756</v>
+        <v>2.779024735370577</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.141417166066831</v>
+        <v>-3.905226399515276</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.089639878093936</v>
+        <v>1.184116184714558</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2415927968402657</v>
+        <v>-0.1249699550455634</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.601607490730256</v>
+        <v>2.671581195807078</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.22441844709211</v>
+        <v>-3.988227680540555</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8947950856844775</v>
+        <v>0.9892713923050995</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2601636813674394</v>
+        <v>-0.1435408395727372</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.428820680014605</v>
+        <v>2.498794385091426</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.065224175035533</v>
+        <v>-3.829033408483979</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.078622455226314</v>
+        <v>1.173098761846936</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2601636813674394</v>
+        <v>-0.1435408395727372</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.548970340733811</v>
+        <v>2.618944045810632</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.151822758016636</v>
+        <v>-3.915631991465081</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.058496048136196</v>
+        <v>1.152972354756817</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2601636813674394</v>
+        <v>-0.1435408395727372</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.563483366836134</v>
+        <v>2.633457071912955</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.113439095458485</v>
+        <v>-3.87724832890693</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.071268954501825</v>
+        <v>1.165745261122447</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2217800188092883</v>
+        <v>-0.105157177014586</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.583933005713393</v>
+        <v>2.653906710790215</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.936322765423319</v>
+        <v>-3.700131998871764</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.138844515361193</v>
+        <v>1.233320821981815</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2217800188092883</v>
+        <v>-0.105157177014586</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.580662034558695</v>
+        <v>2.650635739635517</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.906620641447025</v>
+        <v>-3.670429874895471</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.151408756713624</v>
+        <v>1.245885063334246</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2262501440246016</v>
+        <v>-0.1096273022298994</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578663351191421</v>
+        <v>2.648637056268242</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.727245220208258</v>
+        <v>-3.491054453656703</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.216945900515545</v>
+        <v>1.311422207136167</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.06947338585388296</v>
+        <v>0.04714945594081932</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.666516381400266</v>
+        <v>2.736490086477087</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.772259433728864</v>
+        <v>-3.536068667177309</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.179747670438892</v>
+        <v>1.274223977059514</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.09982228116848757</v>
+        <v>0.01680056062621471</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.629114499543093</v>
+        <v>2.699088204619914</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.039263944001299</v>
+        <v>-3.803073177449744</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.078637428668864</v>
+        <v>1.173113735289486</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2941853192114361</v>
+        <v>-0.1775624774167339</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.518188239056269</v>
+        <v>2.588161944133091</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.328051164460215</v>
+        <v>-4.091860397908659</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9623264623817991</v>
+        <v>1.056802769002421</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3952714393104365</v>
+        <v>-0.2786485975157342</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.456740488893371</v>
+        <v>2.526714193970192</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.327727766413576</v>
+        <v>-4.059384811737887</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9600557831547711</v>
+        <v>1.067392965025047</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3952714393104365</v>
+        <v>-0.2786485975157342</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.454340450447687</v>
+        <v>2.524314155524509</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.553141227993454</v>
+        <v>3.795572831073779</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.652076628436173</v>
+        <v>2.777945815017651</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.327727766413576</v>
+        <v>-4.059384811737887</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9600557831547711</v>
+        <v>1.067392965025047</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3952714393104365</v>
+        <v>-0.2786485975157342</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.64514042542254</v>
+        <v>2.771009612004019</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-24.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-52.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.5%</t>
+          <t>-574.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-61.9%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-269.5%</t>
+          <t>-272.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-242.7%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.9%</t>
+          <t>-242.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.9%</t>
+          <t>-159.5%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612276</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.13391361967919</v>
+        <v>-10.29838598894274</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9164953362517476</v>
+        <v>-0.982284283957167</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.319584068347235</v>
+        <v>-2.364488512853932</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.745676094925334</v>
+        <v>1.718733428221316</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.35195139131037</v>
+        <v>-10.34113665126477</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9992278904197822</v>
+        <v>-0.9949019944015451</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.494354836443134</v>
+        <v>-2.455353951599642</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.645296188552231</v>
+        <v>1.668696719458326</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.27848155964292</v>
+        <v>-10.26766681959732</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.954468256259382</v>
+        <v>-0.950142360241145</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.420885004775686</v>
+        <v>-2.381884119932194</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.704749789046121</v>
+        <v>1.728150319952216</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.45360597702946</v>
+        <v>-10.44279123698387</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.009962802466482</v>
+        <v>-1.005636906448245</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.59600942216223</v>
+        <v>-2.557008537318738</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.614230359361711</v>
+        <v>1.637630890267807</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.68805807104395</v>
+        <v>-10.67724333099836</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.110962804973874</v>
+        <v>-1.106636908955637</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.59600942216223</v>
+        <v>-2.557008537318738</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.607011194460115</v>
+        <v>1.63041172536621</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.97586191558119</v>
+        <v>-10.9650471755356</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.232756533562746</v>
+        <v>-1.228430637544509</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.883813266699468</v>
+        <v>-2.844812381855976</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.427656696963796</v>
+        <v>1.451057227869891</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.20568636274501</v>
+        <v>-11.19487162269942</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.323570522589719</v>
+        <v>-1.319244626571482</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.046460803769628</v>
+        <v>-3.007459918926136</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.331183964560256</v>
+        <v>1.354584495466351</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.43771528248127</v>
+        <v>-11.42690054243568</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.413688361855109</v>
+        <v>-1.409362465836872</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.108473500958052</v>
+        <v>-3.06947261611456</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.296670074876317</v>
+        <v>1.320070605782412</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.38569976851246</v>
+        <v>-11.37488502846687</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.388891820581184</v>
+        <v>-1.384565924562946</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.108473500958052</v>
+        <v>-3.06947261611456</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.300660410562718</v>
+        <v>1.324060941468813</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.52737161023658</v>
+        <v>-11.51655687019099</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.447035784169573</v>
+        <v>-1.442709888151336</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.108473500958052</v>
+        <v>-3.06947261611456</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.299185183663976</v>
+        <v>1.322585714570071</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.47778076581175</v>
+        <v>-11.46696602576615</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.412146036234768</v>
+        <v>-1.40782014021653</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.058882656533218</v>
+        <v>-3.019881771689726</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.343993100483749</v>
+        <v>1.367393631389844</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.27862865857465</v>
+        <v>-11.26781391852906</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.345536326986611</v>
+        <v>-1.341210430968374</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.893560130583404</v>
+        <v>-2.854559245739912</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.430135482406954</v>
+        <v>1.453536013313049</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.05278350585524</v>
+        <v>-11.04196876580965</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.245619192862638</v>
+        <v>-1.241293296844401</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.851633454996241</v>
+        <v>-2.812632570152749</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.46487056079546</v>
+        <v>1.488271091701556</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.92820484951765</v>
+        <v>-10.91739010947205</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.194648585771543</v>
+        <v>-1.190322689753306</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.851633454996241</v>
+        <v>-2.812632570152749</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.466009705351519</v>
+        <v>1.489410236257614</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.98110013756193</v>
+        <v>-10.97028539751634</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.213172926827149</v>
+        <v>-1.208847030808912</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.846678108907795</v>
+        <v>-2.807677224064303</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.471616687166695</v>
+        <v>1.49501721807279</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69719140663318</v>
+        <v>-10.68637666658759</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.093875730217014</v>
+        <v>-1.089549834198777</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.846678108907795</v>
+        <v>-2.807677224064303</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.477350391405331</v>
+        <v>1.500750922311426</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62582501402354</v>
+        <v>-10.61501027397794</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.075066435567019</v>
+        <v>-1.070740539548782</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.775311716298147</v>
+        <v>-2.736310831454654</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.510432964577255</v>
+        <v>1.53383349548335</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36198814681947</v>
+        <v>-10.35117340677387</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9794151699982989</v>
+        <v>-0.9750892739800618</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.775311716298147</v>
+        <v>-2.736310831454654</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.500549483264347</v>
+        <v>1.523950014170443</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.09474634595107</v>
+        <v>-10.08393160590548</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8743530101503141</v>
+        <v>-0.870027114132077</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.775311716298147</v>
+        <v>-2.736310831454654</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.498714922764973</v>
+        <v>1.522115453671069</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.996839307274579</v>
+        <v>-9.986024567228986</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8354905096531784</v>
+        <v>-0.8311646136349413</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.70732596643759</v>
+        <v>-2.668325081594098</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.539206057707846</v>
+        <v>1.562606588613942</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.972885766298621</v>
+        <v>-9.962071026253028</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8252405871173019</v>
+        <v>-0.8209146910990648</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.683372425461633</v>
+        <v>-2.644371540618141</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.554246688438915</v>
+        <v>1.57764721934501</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.708825827975824</v>
+        <v>-9.698011087930231</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7328769279499352</v>
+        <v>-0.7285510319316981</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.419312487138837</v>
+        <v>-2.380311602295345</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.69942233527084</v>
+        <v>1.722822866176935</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.001746204470987</v>
+        <v>-8.990931464425394</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4528321122083012</v>
+        <v>-0.4485062161900641</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.419312487138837</v>
+        <v>-2.380311602295345</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.696635301610539</v>
+        <v>1.720035832516634</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.961561906104796</v>
+        <v>-8.950747166059204</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4364147689739837</v>
+        <v>-0.4320888729557466</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.379128188772646</v>
+        <v>-2.340127303929154</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.721089504518095</v>
+        <v>1.74449003542419</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.881492110566992</v>
+        <v>-8.870677370521399</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4050200295381048</v>
+        <v>-0.4006941335198677</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.299058393234842</v>
+        <v>-2.26005750839135</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.768498203061534</v>
+        <v>1.79189873396763</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.648010888337392</v>
+        <v>-8.6371961482918</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3037031118084128</v>
+        <v>-0.2993772157901757</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.065577171005244</v>
+        <v>-2.026576286161751</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.916511365237146</v>
+        <v>1.939911896143241</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.498344497329878</v>
+        <v>-8.487529757284285</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2467287657183661</v>
+        <v>-0.242402869700129</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.972673679762708</v>
+        <v>-1.933672794919215</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.969361249669708</v>
+        <v>1.992761780575804</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.366069023698991</v>
+        <v>-8.355254283653398</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1984510895189842</v>
+        <v>-0.1941251935007471</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.840398206131821</v>
+        <v>-1.801397321288329</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.044094020595267</v>
+        <v>2.067494551501363</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.175469349025837</v>
+        <v>-8.164654608980245</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1193961589620862</v>
+        <v>-0.1150702629438491</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.649798531458668</v>
+        <v>-1.610797646615176</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.161268886086796</v>
+        <v>2.184669416992891</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.926469550342256</v>
+        <v>-7.915654810296664</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.006889898264994976</v>
+        <v>-0.002564002246757902</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.649798531458668</v>
+        <v>-1.610797646615176</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.174175227310454</v>
+        <v>2.19757575821655</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.032059540115361</v>
+        <v>-8.021244800069768</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1771018237734552</v>
+        <v>-0.1727759277552181</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.755388521231772</v>
+        <v>-1.71638763638828</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.982845303847373</v>
+        <v>2.006245834753469</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.050794442233958</v>
+        <v>-8.039979702188365</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.136051442743808</v>
+        <v>-0.1317255467255709</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.755388521231772</v>
+        <v>-1.71638763638828</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.03138964572446</v>
+        <v>2.054790176630555</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.902854400826358</v>
+        <v>-7.892039660780766</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1967543488689358</v>
+        <v>-0.1924284528506988</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.735067605323215</v>
+        <v>-1.696066720479722</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.923703272581426</v>
+        <v>1.947103803487522</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.80690736714938</v>
+        <v>-7.867811024391793</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1670895216516226</v>
+        <v>-0.1914509845485877</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.639120571646236</v>
+        <v>-1.67183808409075</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.972557506534136</v>
+        <v>1.952926999067427</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.76335896037869</v>
+        <v>-7.824262617621103</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1566307710384396</v>
+        <v>-0.1809922339354046</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.639120571646236</v>
+        <v>-1.67183808409075</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.965596894439043</v>
+        <v>1.945966386972334</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.521210566924831</v>
+        <v>-7.582114224167245</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04530905927575324</v>
+        <v>-0.0696705221727183</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.639120571646236</v>
+        <v>-1.67183808409075</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.980059248820186</v>
+        <v>1.960428741353477</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.457981195156483</v>
+        <v>-7.518884852398896</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.02548519010921879</v>
+        <v>-0.04984665300618385</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.639120571646236</v>
+        <v>-1.67183808409075</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.974591369279381</v>
+        <v>1.954960861812672</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.334690060339352</v>
+        <v>-7.395593717581765</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.02132935782821033</v>
+        <v>-0.003032105068754731</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.515829436829106</v>
+        <v>-1.54854694927362</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.046064144180236</v>
+        <v>2.026433636713527</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.313540861435909</v>
+        <v>-7.374444518678322</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03749001562691312</v>
+        <v>0.01312855272994762</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.494680237925663</v>
+        <v>-1.527397750370176</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.066454641759627</v>
+        <v>2.046824134292919</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.069775419452465</v>
+        <v>-7.130679076694878</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1307769007673412</v>
+        <v>0.1064154378703761</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.494680237925663</v>
+        <v>-1.527397750370176</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.062235350106677</v>
+        <v>2.042604842639969</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.805747352259205</v>
+        <v>-6.866651009501618</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2385124415646613</v>
+        <v>0.2141509786676958</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.292814839109709</v>
+        <v>-1.325532351554223</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.185478903316266</v>
+        <v>2.165848395849557</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.555896958310131</v>
+        <v>-6.616800615552544</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.331194674127993</v>
+        <v>0.3068332112310279</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.292814839109709</v>
+        <v>-1.325532351554223</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.178220978299968</v>
+        <v>2.158590470833259</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.380004865842698</v>
+        <v>-6.440908523085112</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4051506346356146</v>
+        <v>0.3807891717386496</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.292814839109709</v>
+        <v>-1.325532351554223</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181820101820616</v>
+        <v>2.162189594353908</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.208558402820235</v>
+        <v>-6.269462060062648</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4870567258991536</v>
+        <v>0.4626952630021886</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.121368376087246</v>
+        <v>-1.15408588853176</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.298015485688648</v>
+        <v>2.27838497822194</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.983525403151412</v>
+        <v>-6.044429060393825</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5760904033829801</v>
+        <v>0.5517289404860146</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8963353764184229</v>
+        <v>-0.9290528888629367</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.432055763106239</v>
+        <v>2.41242525563953</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.768891025515005</v>
+        <v>-5.829794682757418</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6666389554918601</v>
+        <v>0.6422774925948946</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6817009987820161</v>
+        <v>-0.7144185112265299</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.5655311907424</v>
+        <v>2.545900683275692</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.675890984309107</v>
+        <v>-5.73679464155152</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6850332307580151</v>
+        <v>0.6606717678610496</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6817009987820161</v>
+        <v>-0.7144185112265299</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.546725449526196</v>
+        <v>2.527094942059487</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.435460487504247</v>
+        <v>-5.49636414474666</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7829485061048365</v>
+        <v>0.7585870432078714</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4412705019771558</v>
+        <v>-0.4739880144216696</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.692726824233989</v>
+        <v>2.673096316767281</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.363217919333052</v>
+        <v>-5.424121576575465</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8157748472081345</v>
+        <v>0.7914133843111695</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4412705019771558</v>
+        <v>-0.4739880144216696</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.69665613806881</v>
+        <v>2.677025630602101</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.247278069707867</v>
+        <v>-5.30818172695028</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8628293709755486</v>
+        <v>0.8384679080785835</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3644487709610319</v>
+        <v>-0.3971662834055457</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.743427760595824</v>
+        <v>2.723797253129115</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.004622481284704</v>
+        <v>-5.065526138527117</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9568896775648073</v>
+        <v>0.9325282146678422</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3644487709610319</v>
+        <v>-0.3971662834055457</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.740425831815817</v>
+        <v>2.720795324349109</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.784601683247693</v>
+        <v>-4.845505340490107</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.046477033790226</v>
+        <v>1.02211557089326</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2232289258930517</v>
+        <v>-0.2559464383375655</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.82673677586722</v>
+        <v>2.807106268400511</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.651733994184416</v>
+        <v>-4.712637651426829</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.11551829221736</v>
+        <v>1.091156829320395</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2232289258930517</v>
+        <v>-0.2559464383375655</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.842630958669043</v>
+        <v>2.823000451202335</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.492218890665046</v>
+        <v>-4.553122547907459</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.18047017806541</v>
+        <v>1.156108715168445</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06371382237368173</v>
+        <v>-0.09643133481819555</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.939485865220967</v>
+        <v>2.919855357754258</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.347546745565309</v>
+        <v>-4.408450402807722</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.248427138666745</v>
+        <v>1.224065675769779</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.08095832272605569</v>
+        <v>0.04824081028154187</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.036377254842249</v>
+        <v>3.01674674737554</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.407421572923001</v>
+        <v>-4.468325230165414</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.210514699125093</v>
+        <v>1.186153236228128</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.02108349536836357</v>
+        <v>-0.01163401707615025</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.98648984982906</v>
+        <v>2.966859342362351</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.320622075143993</v>
+        <v>-4.381525732386406</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.267634991559263</v>
+        <v>1.243273528662298</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.02108349536836357</v>
+        <v>-0.01163401707615025</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.008890343151626</v>
+        <v>2.989259835684917</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.323091781605799</v>
+        <v>-4.383995438848212</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.266719510347953</v>
+        <v>1.242358047450987</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.0186137889065574</v>
+        <v>-0.01410372353795641</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.007480920647954</v>
+        <v>2.987850413181246</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.391461967929809</v>
+        <v>-4.452365625172222</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.250378358293051</v>
+        <v>1.226016895396085</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02788948794277235</v>
+        <v>-0.004828024501741468</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.024053262544385</v>
+        <v>3.004422755077677</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.270045538303332</v>
+        <v>-4.330949195545745</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.289381638775533</v>
+        <v>1.265020175878567</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02788948794277235</v>
+        <v>-0.004828024501741468</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.014489971176276</v>
+        <v>2.994859463709568</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.301038697632038</v>
+        <v>-4.361942354874451</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.101693940084437</v>
+        <v>1.077332477187472</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02788948794277235</v>
+        <v>-0.004828024501741468</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.839199536216663</v>
+        <v>2.819569028749955</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.125564437839568</v>
+        <v>-4.186468095081981</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.176450875993213</v>
+        <v>1.152089413096248</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02788948794277235</v>
+        <v>-0.004828024501741468</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.843766768208451</v>
+        <v>2.824136260741743</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.236500690480817</v>
+        <v>-4.29740434772323</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.10781840369792</v>
+        <v>1.083456940800955</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02788948794277235</v>
+        <v>-0.004828024501741468</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.819508796969658</v>
+        <v>2.79987828950295</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.43952726802405</v>
+        <v>-4.500430925266463</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.029739157900533</v>
+        <v>1.005377695003567</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.175137089600461</v>
+        <v>-0.2078546020449749</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.700824235663624</v>
+        <v>2.681193728196915</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.281601669088757</v>
+        <v>-4.405826194771184</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.103081783906782</v>
+        <v>1.053391973633811</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.175137089600461</v>
+        <v>-0.1132498715496962</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.710996622095756</v>
+        <v>2.748128952926215</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.195358206062379</v>
+        <v>-4.319582731744807</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.132525439691193</v>
+        <v>1.082835629418223</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.175137089600461</v>
+        <v>-0.1132498715496962</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.705942892669616</v>
+        <v>2.743075223500075</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.196541290713441</v>
+        <v>-4.270562878045027</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.123827981275294</v>
+        <v>1.09421934634266</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1807801380669726</v>
+        <v>-0.08669952981990925</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.694332839034235</v>
+        <v>2.750781203982473</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.073413583719358</v>
+        <v>-4.147435171050944</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.173630937106029</v>
+        <v>1.144022302173395</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1807801380669726</v>
+        <v>-0.08669952981990925</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.694884712067336</v>
+        <v>2.751333077015574</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.980603102268498</v>
+        <v>-4.054624689600084</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.140027821577739</v>
+        <v>1.110419186645104</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08796965661611322</v>
+        <v>0.006110951630950101</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.679843692829218</v>
+        <v>2.736292057777455</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.932040050047468</v>
+        <v>-4.006061637379053</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.161326518390752</v>
+        <v>1.131717883458117</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.03940660439508303</v>
+        <v>0.05467400385198029</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.710855000086437</v>
+        <v>2.767303365034675</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.819368831811218</v>
+        <v>-3.893390419142803</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.201470714196975</v>
+        <v>1.17186207926434</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07326461384116717</v>
+        <v>0.1673452220882305</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.77353343953991</v>
+        <v>2.829981804488148</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.706991830628545</v>
+        <v>-3.781013417960131</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.251912810500711</v>
+        <v>1.222304175568077</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07326461384116717</v>
+        <v>0.1673452220882305</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.779024735370577</v>
+        <v>2.835473100318815</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.905226399515276</v>
+        <v>-3.979247986846861</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.184116184714558</v>
+        <v>1.154507549781923</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1249699550455634</v>
+        <v>-0.03088934679850008</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.671581195807078</v>
+        <v>2.728029560755316</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.988227680540555</v>
+        <v>-4.06224926787214</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9892713923050995</v>
+        <v>0.9596627573724654</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1435408395727372</v>
+        <v>-0.04946023132567384</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.498794385091426</v>
+        <v>2.555242750039665</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.829033408483979</v>
+        <v>-3.903054995815564</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.173098761846936</v>
+        <v>1.143490126914302</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1435408395727372</v>
+        <v>-0.04946023132567384</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.618944045810632</v>
+        <v>2.67539241075887</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.915631991465081</v>
+        <v>-3.989653578796667</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.152972354756817</v>
+        <v>1.123363719824183</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1435408395727372</v>
+        <v>-0.04946023132567384</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.633457071912955</v>
+        <v>2.689905436861193</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.87724832890693</v>
+        <v>-3.951269916238516</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.165745261122447</v>
+        <v>1.136136626189812</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.105157177014586</v>
+        <v>-0.01107656876752267</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.653906710790215</v>
+        <v>2.710355075738453</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.700131998871764</v>
+        <v>-3.77415358620335</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.233320821981815</v>
+        <v>1.203712187049181</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.105157177014586</v>
+        <v>-0.01107656876752267</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.650635739635517</v>
+        <v>2.707084104583755</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.670429874895471</v>
+        <v>-3.744451462227056</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.245885063334246</v>
+        <v>1.216276428401611</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1096273022298994</v>
+        <v>-0.01554669398283604</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.648637056268242</v>
+        <v>2.70508542121648</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.491054453656703</v>
+        <v>-3.565076040988288</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.311422207136167</v>
+        <v>1.281813572203533</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04714945594081932</v>
+        <v>0.1412300641878826</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.736490086477087</v>
+        <v>2.792938451425325</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.536068667177309</v>
+        <v>-3.610090254508894</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.274223977059514</v>
+        <v>1.24461534212688</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01680056062621471</v>
+        <v>0.110881168873278</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.699088204619914</v>
+        <v>2.755536569568152</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.803073177449744</v>
+        <v>-3.877094764781329</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.173113735289486</v>
+        <v>1.143505100356852</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1775624774167339</v>
+        <v>-0.08348186916967054</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.588161944133091</v>
+        <v>2.644610309081329</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.091860397908659</v>
+        <v>-4.165881985240245</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.056802769002421</v>
+        <v>1.027194134069787</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2786485975157342</v>
+        <v>-0.1845679892686709</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.526714193970192</v>
+        <v>2.58316255891843</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.059384811737887</v>
+        <v>-4.133406399069472</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.067392965025047</v>
+        <v>1.037784330092413</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2786485975157342</v>
+        <v>-0.1845679892686709</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.524314155524509</v>
+        <v>2.580762520472747</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.795572831073779</v>
+        <v>3.854529328865257</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.777945815017651</v>
+        <v>2.871987752641979</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.059384811737887</v>
+        <v>-4.133406399069472</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.067392965025047</v>
+        <v>1.037784330092413</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2786485975157342</v>
+        <v>-0.1845679892686709</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.771009612004019</v>
+        <v>2.865051549628347</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.2%</t>
+          <t>445.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.9%</t>
+          <t>-573.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.4%</t>
+          <t>-271.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.4%</t>
+          <t>-254.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.34113665126477</v>
+        <v>-10.3374263415806</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9949019944015451</v>
+        <v>-0.9934178705278751</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.455353951599642</v>
+        <v>-2.450500270270166</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.668696719458326</v>
+        <v>1.671608928256011</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.26766681959732</v>
+        <v>-10.26395650991315</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.950142360241145</v>
+        <v>-0.948658236367474</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381884119932194</v>
+        <v>-2.377030438602718</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.728150319952216</v>
+        <v>1.731062528749902</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.44279123698387</v>
+        <v>-10.43908092729969</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.005636906448245</v>
+        <v>-1.004152782574574</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.557008537318738</v>
+        <v>-2.552154855989262</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.637630890267807</v>
+        <v>1.640543099065492</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.67724333099836</v>
+        <v>-10.67353302131418</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.106636908955637</v>
+        <v>-1.105152785081966</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.557008537318738</v>
+        <v>-2.552154855989262</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.63041172536621</v>
+        <v>1.633323934163896</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.9650471755356</v>
+        <v>-10.96133686585142</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.228430637544509</v>
+        <v>-1.226946513670838</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.844812381855976</v>
+        <v>-2.8399587005265</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.451057227869891</v>
+        <v>1.453969436667577</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.19487162269942</v>
+        <v>-11.19116131301524</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.319244626571482</v>
+        <v>-1.317760502697812</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.007459918926136</v>
+        <v>-3.00260623759666</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.354584495466351</v>
+        <v>1.357496704264037</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.42690054243568</v>
+        <v>-11.42319023275151</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.409362465836872</v>
+        <v>-1.407878341963201</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.06947261611456</v>
+        <v>-3.064618934785083</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.320070605782412</v>
+        <v>1.322982814580098</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.37488502846687</v>
+        <v>-11.37117471878269</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.384565924562946</v>
+        <v>-1.383081800689276</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.06947261611456</v>
+        <v>-3.064618934785083</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.324060941468813</v>
+        <v>1.326973150266499</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.51655687019099</v>
+        <v>-11.51284656050681</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.442709888151336</v>
+        <v>-1.441225764277665</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.06947261611456</v>
+        <v>-3.064618934785083</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.322585714570071</v>
+        <v>1.325497923367757</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.46696602576615</v>
+        <v>-11.46325571608198</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.40782014021653</v>
+        <v>-1.40633601634286</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.019881771689726</v>
+        <v>-3.01502809036025</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.367393631389844</v>
+        <v>1.37030584018753</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.26781391852906</v>
+        <v>-11.26410360884488</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.341210430968374</v>
+        <v>-1.339726307094703</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.854559245739912</v>
+        <v>-2.849705564410436</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.453536013313049</v>
+        <v>1.456448222110734</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.04196876580965</v>
+        <v>-11.03825845612547</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.241293296844401</v>
+        <v>-1.23980917297073</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.812632570152749</v>
+        <v>-2.807778888823273</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.488271091701556</v>
+        <v>1.491183300499241</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.91739010947205</v>
+        <v>-10.91367979978788</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.190322689753306</v>
+        <v>-1.188838565879635</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.812632570152749</v>
+        <v>-2.807778888823273</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.489410236257614</v>
+        <v>1.4923224450553</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.97028539751634</v>
+        <v>-10.96657508783216</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.208847030808912</v>
+        <v>-1.207362906935241</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.807677224064303</v>
+        <v>-2.802823542734826</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.49501721807279</v>
+        <v>1.497929426870476</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.68637666658759</v>
+        <v>-10.68266635690341</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.089549834198777</v>
+        <v>-1.088065710325106</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.807677224064303</v>
+        <v>-2.802823542734826</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.500750922311426</v>
+        <v>1.503663131109112</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.61501027397794</v>
+        <v>-10.61129996429377</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.070740539548782</v>
+        <v>-1.069256415675111</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.736310831454654</v>
+        <v>-2.731457150125178</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.53383349548335</v>
+        <v>1.536745704281036</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.35117340677387</v>
+        <v>-10.3474630970897</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9750892739800618</v>
+        <v>-0.9736051501063918</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.736310831454654</v>
+        <v>-2.731457150125178</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.523950014170443</v>
+        <v>1.526862222968128</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.08393160590548</v>
+        <v>-10.0802212962213</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.870027114132077</v>
+        <v>-0.8685429902584061</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.736310831454654</v>
+        <v>-2.731457150125178</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.522115453671069</v>
+        <v>1.525027662468754</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.986024567228986</v>
+        <v>-9.982314257544809</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8311646136349413</v>
+        <v>-0.8296804897612708</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.668325081594098</v>
+        <v>-2.663471400264622</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.562606588613942</v>
+        <v>1.565518797411628</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.962071026253028</v>
+        <v>-9.958360716568851</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8209146910990648</v>
+        <v>-0.8194305672253939</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.644371540618141</v>
+        <v>-2.639517859288664</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.57764721934501</v>
+        <v>1.580559428142696</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.698011087930231</v>
+        <v>-9.694300778246054</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7285510319316981</v>
+        <v>-0.7270669080580272</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.380311602295345</v>
+        <v>-2.375457920965868</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.722822866176935</v>
+        <v>1.725735074974621</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.990931464425394</v>
+        <v>-8.987221154741217</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4485062161900641</v>
+        <v>-0.4470220923163932</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.380311602295345</v>
+        <v>-2.375457920965868</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.720035832516634</v>
+        <v>1.72294804131432</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.950747166059204</v>
+        <v>-8.947036856375027</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4320888729557466</v>
+        <v>-0.4306047490820757</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.340127303929154</v>
+        <v>-2.335273622599678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.74449003542419</v>
+        <v>1.747402244221876</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.870677370521399</v>
+        <v>-8.866967060837222</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4006941335198677</v>
+        <v>-0.3992100096461968</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.26005750839135</v>
+        <v>-2.255203827061874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.79189873396763</v>
+        <v>1.794810942765315</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.6371961482918</v>
+        <v>-8.633485838607623</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2993772157901757</v>
+        <v>-0.2978930919165048</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.026576286161751</v>
+        <v>-2.021722604832275</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.939911896143241</v>
+        <v>1.942824104940927</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.487529757284285</v>
+        <v>-8.483819447600109</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.242402869700129</v>
+        <v>-0.2409187458264581</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.933672794919215</v>
+        <v>-1.928819113589739</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.992761780575804</v>
+        <v>1.995673989373489</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.355254283653398</v>
+        <v>-8.351543973969221</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1941251935007471</v>
+        <v>-0.1926410696270762</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.801397321288329</v>
+        <v>-1.796543639958852</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.067494551501363</v>
+        <v>2.070406760299048</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.164654608980245</v>
+        <v>-8.160944299296068</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1150702629438491</v>
+        <v>-0.1135861390701782</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.610797646615176</v>
+        <v>-1.605943965285699</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.184669416992891</v>
+        <v>2.187581625790577</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.915654810296664</v>
+        <v>-7.911944500612487</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.002564002246757902</v>
+        <v>-0.001079878373086984</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.610797646615176</v>
+        <v>-1.605943965285699</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.19757575821655</v>
+        <v>2.200487967014236</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.021244800069768</v>
+        <v>-8.017534490385591</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1727759277552181</v>
+        <v>-0.1712918038815476</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.71638763638828</v>
+        <v>-1.711533955058804</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.006245834753469</v>
+        <v>2.009158043551154</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.039979702188365</v>
+        <v>-8.036269392504188</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1317255467255709</v>
+        <v>-0.1302414228519</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.71638763638828</v>
+        <v>-1.711533955058804</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.054790176630555</v>
+        <v>2.05770238542824</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.892039660780766</v>
+        <v>-7.888329351096589</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1924284528506988</v>
+        <v>-0.1909443289770278</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.696066720479722</v>
+        <v>-1.691213039150246</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.947103803487522</v>
+        <v>1.950016012285208</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.867811024391793</v>
+        <v>-7.864100714707616</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1914509845485877</v>
+        <v>-0.1899668606749172</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.67183808409075</v>
+        <v>-1.666984402761274</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.952926999067427</v>
+        <v>1.955839207865113</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.824262617621103</v>
+        <v>-7.820552307936926</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1809922339354046</v>
+        <v>-0.1795081100617342</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.67183808409075</v>
+        <v>-1.666984402761274</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.945966386972334</v>
+        <v>1.94887859577002</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.582114224167245</v>
+        <v>-7.578403914483068</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.0696705221727183</v>
+        <v>-0.06818639829904782</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.67183808409075</v>
+        <v>-1.666984402761274</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.960428741353477</v>
+        <v>1.963340950151163</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.518884852398896</v>
+        <v>-7.515174542714719</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.04984665300618385</v>
+        <v>-0.04836252913251338</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.67183808409075</v>
+        <v>-1.666984402761274</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.954960861812672</v>
+        <v>1.957873070610358</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.395593717581765</v>
+        <v>-7.391883407897589</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.003032105068754731</v>
+        <v>-0.001547981195084258</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.54854694927362</v>
+        <v>-1.543693267944144</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.026433636713527</v>
+        <v>2.029345845511213</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.374444518678322</v>
+        <v>-7.370734208994145</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.01312855272994762</v>
+        <v>0.01461267660361854</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.527397750370176</v>
+        <v>-1.5225440690407</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.046824134292919</v>
+        <v>2.049736343090604</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.130679076694878</v>
+        <v>-7.126968767010701</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1064154378703761</v>
+        <v>0.107899561744047</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.527397750370176</v>
+        <v>-1.5225440690407</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.042604842639969</v>
+        <v>2.045517051437655</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.866651009501618</v>
+        <v>-6.862940699817441</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2141509786676958</v>
+        <v>0.2156351025413668</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.325532351554223</v>
+        <v>-1.320678670224747</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.165848395849557</v>
+        <v>2.168760604647243</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.616800615552544</v>
+        <v>-6.613090305868367</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3068332112310279</v>
+        <v>0.3083173351046988</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.325532351554223</v>
+        <v>-1.320678670224747</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.158590470833259</v>
+        <v>2.161502679630945</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.440908523085112</v>
+        <v>-6.437198213400935</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3807891717386496</v>
+        <v>0.38227329561232</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.325532351554223</v>
+        <v>-1.320678670224747</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.162189594353908</v>
+        <v>2.165101803151594</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.269462060062648</v>
+        <v>-6.265751750378471</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4626952630021886</v>
+        <v>0.4641793868758595</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.15408588853176</v>
+        <v>-1.149232207202283</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.27838497822194</v>
+        <v>2.281297187019625</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.044429060393825</v>
+        <v>-6.040718750709648</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5517289404860146</v>
+        <v>0.5532130643596855</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9290528888629367</v>
+        <v>-0.9241992075334605</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.41242525563953</v>
+        <v>2.415337464437216</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.829794682757418</v>
+        <v>-5.826084373073241</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6422774925948946</v>
+        <v>0.6437616164685656</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7144185112265299</v>
+        <v>-0.7095648298970537</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.545900683275692</v>
+        <v>2.548812892073378</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.73679464155152</v>
+        <v>-5.733084331867343</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6606717678610496</v>
+        <v>0.6621558917347206</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7144185112265299</v>
+        <v>-0.7095648298970537</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.527094942059487</v>
+        <v>2.530007150857173</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.49636414474666</v>
+        <v>-5.492653835062483</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7585870432078714</v>
+        <v>0.7600711670815419</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4739880144216696</v>
+        <v>-0.4691343330921934</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.673096316767281</v>
+        <v>2.676008525564967</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.424121576575465</v>
+        <v>-5.420411266891288</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7914133843111695</v>
+        <v>0.7928975081848399</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4739880144216696</v>
+        <v>-0.4691343330921934</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.677025630602101</v>
+        <v>2.679937839399787</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.30818172695028</v>
+        <v>-5.304471417266103</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8384679080785835</v>
+        <v>0.839952031952254</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3971662834055457</v>
+        <v>-0.3923126020760695</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.723797253129115</v>
+        <v>2.726709461926801</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.065526138527117</v>
+        <v>-5.06181582884294</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9325282146678422</v>
+        <v>0.9340123385415127</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3971662834055457</v>
+        <v>-0.3923126020760695</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.720795324349109</v>
+        <v>2.723707533146795</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.845505340490107</v>
+        <v>-4.84179503080593</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.02211557089326</v>
+        <v>1.023599694766931</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2559464383375655</v>
+        <v>-0.2510927570080893</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.807106268400511</v>
+        <v>2.810018477198197</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.712637651426829</v>
+        <v>-4.708927341742652</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.091156829320395</v>
+        <v>1.092640953194066</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2559464383375655</v>
+        <v>-0.2510927570080893</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.823000451202335</v>
+        <v>2.82591266000002</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.553122547907459</v>
+        <v>-4.549412238223282</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.156108715168445</v>
+        <v>1.157592839042115</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.09643133481819555</v>
+        <v>-0.09157765348871938</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.919855357754258</v>
+        <v>2.922767566551944</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.408450402807722</v>
+        <v>-4.404740093123545</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.224065675769779</v>
+        <v>1.22554979964345</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.04824081028154187</v>
+        <v>0.05309449161101804</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.01674674737554</v>
+        <v>3.019658956173227</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.468325230165414</v>
+        <v>-4.464614920481237</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.186153236228128</v>
+        <v>1.187637360101799</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.01163401707615025</v>
+        <v>-0.006780335746674082</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.966859342362351</v>
+        <v>2.969771551160037</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.381525732386406</v>
+        <v>-4.377815422702229</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.243273528662298</v>
+        <v>1.244757652535968</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.01163401707615025</v>
+        <v>-0.006780335746674082</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.989259835684917</v>
+        <v>2.992172044482603</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.383995438848212</v>
+        <v>-4.380285129164035</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.242358047450987</v>
+        <v>1.243842171324658</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.01410372353795641</v>
+        <v>-0.009250042208480247</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.987850413181246</v>
+        <v>2.990762621978932</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.452365625172222</v>
+        <v>-4.448655315488045</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.226016895396085</v>
+        <v>1.227501019269756</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.004828024501741468</v>
+        <v>2.565682773469913e-05</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.004422755077677</v>
+        <v>3.007334963875362</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.330949195545745</v>
+        <v>-4.327238885861568</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.265020175878567</v>
+        <v>1.266504299752238</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.004828024501741468</v>
+        <v>2.565682773469913e-05</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.994859463709568</v>
+        <v>2.997771672507254</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.361942354874451</v>
+        <v>-4.358232045190274</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.077332477187472</v>
+        <v>1.078816601061143</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.004828024501741468</v>
+        <v>2.565682773469913e-05</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.819569028749955</v>
+        <v>2.82248123754764</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.186468095081981</v>
+        <v>-4.182757785397804</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.152089413096248</v>
+        <v>1.153573536969918</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.004828024501741468</v>
+        <v>2.565682773469913e-05</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.824136260741743</v>
+        <v>2.827048469539428</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.29740434772323</v>
+        <v>-4.293694038039053</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.083456940800955</v>
+        <v>1.084941064674626</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.004828024501741468</v>
+        <v>2.565682773469913e-05</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.79987828950295</v>
+        <v>2.802790498300635</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.500430925266463</v>
+        <v>-4.496720615582286</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.005377695003567</v>
+        <v>1.006861818877238</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2078546020449749</v>
+        <v>-0.2030009207154987</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.681193728196915</v>
+        <v>2.684105936994601</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.405826194771184</v>
+        <v>-4.338795016646993</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.053391973633811</v>
+        <v>1.080204444883488</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1132498715496962</v>
+        <v>-0.2030009207154987</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.748128952926215</v>
+        <v>2.694278323426733</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.319582731744807</v>
+        <v>-4.252551553620616</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.082835629418223</v>
+        <v>1.109648100667899</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1132498715496962</v>
+        <v>-0.2030009207154987</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.743075223500075</v>
+        <v>2.689224594000593</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.270562878045027</v>
+        <v>-4.253734638271677</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.09421934634266</v>
+        <v>1.100950642252</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.08669952981990925</v>
+        <v>-0.2086439691820102</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.750781203982473</v>
+        <v>2.677614540365212</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.147435171050944</v>
+        <v>-4.130606931277594</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.144022302173395</v>
+        <v>1.150753598082735</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.08669952981990925</v>
+        <v>-0.2086439691820102</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.751333077015574</v>
+        <v>2.678166413398314</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.054624689600084</v>
+        <v>-4.037796449826734</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.110419186645104</v>
+        <v>1.117150482554444</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.006110951630950101</v>
+        <v>-0.1158334877311509</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.736292057777455</v>
+        <v>2.663125394160195</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.006061637379053</v>
+        <v>-3.989233397605704</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.131717883458117</v>
+        <v>1.138449179367457</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.05467400385198029</v>
+        <v>-0.06727043551012069</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.767303365034675</v>
+        <v>2.694136701417414</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.893390419142803</v>
+        <v>-3.876562179369454</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.17186207926434</v>
+        <v>1.17859337517368</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1673452220882305</v>
+        <v>0.04540078272612952</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.829981804488148</v>
+        <v>2.756815140870887</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.781013417960131</v>
+        <v>-3.764185178186781</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.222304175568077</v>
+        <v>1.229035471477417</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1673452220882305</v>
+        <v>0.04540078272612952</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.835473100318815</v>
+        <v>2.762306436701554</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.979247986846861</v>
+        <v>-3.962419747073512</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.154507549781923</v>
+        <v>1.161238845691263</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.03088934679850008</v>
+        <v>-0.1528337861606011</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.728029560755316</v>
+        <v>2.654862897138055</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.06224926787214</v>
+        <v>-4.04542102809879</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9596627573724654</v>
+        <v>0.9663940532818054</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.04946023132567384</v>
+        <v>-0.1714046706877748</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.555242750039665</v>
+        <v>2.482076086422404</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.903054995815564</v>
+        <v>-3.886226756042214</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.143490126914302</v>
+        <v>1.150221422823642</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.04946023132567384</v>
+        <v>-0.1714046706877748</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.67539241075887</v>
+        <v>2.60222574714161</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.989653578796667</v>
+        <v>-3.972825339023317</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.123363719824183</v>
+        <v>1.130095015733523</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.04946023132567384</v>
+        <v>-0.1714046706877748</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.689905436861193</v>
+        <v>2.616738773243933</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.951269916238516</v>
+        <v>-3.934441676465166</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.136136626189812</v>
+        <v>1.142867922099152</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.01107656876752267</v>
+        <v>-0.1330210081296236</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.710355075738453</v>
+        <v>2.637188412121192</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.77415358620335</v>
+        <v>-3.75732534643</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.203712187049181</v>
+        <v>1.210443482958521</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.01107656876752267</v>
+        <v>-0.1330210081296236</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.707084104583755</v>
+        <v>2.633917440966494</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.744451462227056</v>
+        <v>-3.727623222453706</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.216276428401611</v>
+        <v>1.223007724310951</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01554669398283604</v>
+        <v>-0.137491133344937</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.70508542121648</v>
+        <v>2.631918757599219</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.565076040988288</v>
+        <v>-3.548247801214938</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.281813572203533</v>
+        <v>1.288544868112873</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1412300641878826</v>
+        <v>0.01928562482578167</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.792938451425325</v>
+        <v>2.719771787808065</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.610090254508894</v>
+        <v>-3.593262014735544</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.24461534212688</v>
+        <v>1.25134663803622</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.110881168873278</v>
+        <v>-0.01106327048882294</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.755536569568152</v>
+        <v>2.682369905950892</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.877094764781329</v>
+        <v>-3.86026652500798</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.143505100356852</v>
+        <v>1.150236396266192</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08348186916967054</v>
+        <v>-0.2054263085317715</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.644610309081329</v>
+        <v>2.571443645464068</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.165881985240245</v>
+        <v>-4.149053745466895</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.027194134069787</v>
+        <v>1.033925429979127</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1845679892686709</v>
+        <v>-0.3065124286307719</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.58316255891843</v>
+        <v>2.50999589530117</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.133406399069472</v>
+        <v>-4.116578159296123</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.037784330092413</v>
+        <v>1.044515626001753</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1845679892686709</v>
+        <v>-0.3065124286307719</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.580762520472747</v>
+        <v>2.507595856855486</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,13 +46677,13 @@
         <v>2.871987752641979</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.133406399069472</v>
+        <v>-4.116578159296123</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.037784330092413</v>
+        <v>1.044515626001753</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.1845679892686709</v>
+        <v>-0.3065124286307719</v>
       </c>
       <c r="G1962" t="n">
         <v>2.865051549628347</v>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-40.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>133.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.6%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.3%</t>
+          <t>439.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.2%</t>
+          <t>-594.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,57 +1140,57 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-64.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.8%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>-147.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-254.6%</t>
+          <t>-281.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.5%</t>
+          <t>-208.6%</t>
         </is>
       </c>
     </row>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.3374263415806</v>
+        <v>-10.51642376057391</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9934178705278751</v>
+        <v>-1.065016838125203</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.450500270270166</v>
+        <v>-2.539259280949831</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671608928256011</v>
+        <v>1.618353521848213</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.26395650991315</v>
+        <v>-10.54142628370588</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.948658236367474</v>
+        <v>-1.059646145884569</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.377030438602718</v>
+        <v>-2.564261804081802</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731062528749902</v>
+        <v>1.618723709462451</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.43908092729969</v>
+        <v>-10.71655070109243</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.004152782574574</v>
+        <v>-1.11514069209167</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.552154855989262</v>
+        <v>-2.739386221468346</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640543099065492</v>
+        <v>1.528204279778042</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.67353302131418</v>
+        <v>-10.95100279510692</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.105152785081966</v>
+        <v>-1.216140694599062</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.552154855989262</v>
+        <v>-2.739386221468346</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633323934163896</v>
+        <v>1.520985114876445</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.96133686585142</v>
+        <v>-11.23880663964416</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.226946513670838</v>
+        <v>-1.337934423187934</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.8399587005265</v>
+        <v>-3.027190066005584</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.453969436667577</v>
+        <v>1.341630617380126</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.19116131301524</v>
+        <v>-11.46863108680798</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.317760502697812</v>
+        <v>-1.428748412214907</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.00260623759666</v>
+        <v>-3.189837603075745</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.357496704264037</v>
+        <v>1.245157884976587</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.42319023275151</v>
+        <v>-11.70066000654424</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.407878341963201</v>
+        <v>-1.518866251480298</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.064618934785083</v>
+        <v>-3.251850300264168</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.322982814580098</v>
+        <v>1.210643995292647</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.37117471878269</v>
+        <v>-11.64864449257543</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.383081800689276</v>
+        <v>-1.494069710206371</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.064618934785083</v>
+        <v>-3.251850300264168</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.326973150266499</v>
+        <v>1.214634330979048</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.51284656050681</v>
+        <v>-11.79031633429955</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.441225764277665</v>
+        <v>-1.55221367379476</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.064618934785083</v>
+        <v>-3.251850300264168</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.325497923367757</v>
+        <v>1.213159104080306</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.46325571608198</v>
+        <v>-11.74072548987472</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.40633601634286</v>
+        <v>-1.517323925859955</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.01502809036025</v>
+        <v>-3.202259455839334</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.37030584018753</v>
+        <v>1.257967020900079</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.26410360884488</v>
+        <v>-11.54157338263762</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.339726307094703</v>
+        <v>-1.450714216611798</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.849705564410436</v>
+        <v>-3.036936929889521</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.456448222110734</v>
+        <v>1.344109402823284</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.03825845612547</v>
+        <v>-11.31572822991821</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.23980917297073</v>
+        <v>-1.350797082487826</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.807778888823273</v>
+        <v>-2.995010254302357</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.491183300499241</v>
+        <v>1.378844481211791</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.91367979978788</v>
+        <v>-11.19114957358062</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.188838565879635</v>
+        <v>-1.29982647539673</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.807778888823273</v>
+        <v>-2.995010254302357</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.4923224450553</v>
+        <v>1.379983625767849</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.96657508783216</v>
+        <v>-11.2440448616249</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.207362906935241</v>
+        <v>-1.318350816452337</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.802823542734826</v>
+        <v>-2.990054908213911</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.497929426870476</v>
+        <v>1.385590607583025</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.68266635690341</v>
+        <v>-10.96013613069615</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.088065710325106</v>
+        <v>-1.199053619842201</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.802823542734826</v>
+        <v>-2.990054908213911</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.503663131109112</v>
+        <v>1.391324311821661</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.61129996429377</v>
+        <v>-10.88876973808651</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.069256415675111</v>
+        <v>-1.180244325192207</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.731457150125178</v>
+        <v>-2.918688515604263</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.536745704281036</v>
+        <v>1.424406884993585</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.3474630970897</v>
+        <v>-10.62493287088244</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9736051501063918</v>
+        <v>-1.084593059623487</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.731457150125178</v>
+        <v>-2.918688515604263</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.526862222968128</v>
+        <v>1.414523403680677</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.0802212962213</v>
+        <v>-10.35769107001404</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8685429902584061</v>
+        <v>-0.9795308997755012</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.731457150125178</v>
+        <v>-2.918688515604263</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.525027662468754</v>
+        <v>1.412688843181304</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.982314257544809</v>
+        <v>-10.25978403133755</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8296804897612708</v>
+        <v>-0.940668399278366</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.663471400264622</v>
+        <v>-2.850702765743707</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.565518797411628</v>
+        <v>1.453179978124177</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.958360716568851</v>
+        <v>-10.23583049036159</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8194305672253939</v>
+        <v>-0.930418476742489</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.639517859288664</v>
+        <v>-2.826749224767749</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.580559428142696</v>
+        <v>1.468220608855245</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.694300778246054</v>
+        <v>-9.971770552038793</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7270669080580272</v>
+        <v>-0.8380548175751228</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.375457920965868</v>
+        <v>-2.562689286444953</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.725735074974621</v>
+        <v>1.61339625568717</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.987221154741217</v>
+        <v>-9.264690928533955</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4470220923163932</v>
+        <v>-0.5580100018334884</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.375457920965868</v>
+        <v>-2.562689286444953</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.72294804131432</v>
+        <v>1.610609222026869</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.947036856375027</v>
+        <v>-9.224506630167765</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4306047490820757</v>
+        <v>-0.5415926585991708</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.335273622599678</v>
+        <v>-2.522504988078762</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.747402244221876</v>
+        <v>1.635063424934425</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.866967060837222</v>
+        <v>-9.14443683462996</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3992100096461968</v>
+        <v>-0.5101979191632924</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.255203827061874</v>
+        <v>-2.442435192540958</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.794810942765315</v>
+        <v>1.682472123477865</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.633485838607623</v>
+        <v>-8.910955612400361</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2978930919165048</v>
+        <v>-0.4088810014336</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.021722604832275</v>
+        <v>-2.20895397031136</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.942824104940927</v>
+        <v>1.830485285653476</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.483819447600109</v>
+        <v>-8.761289221392847</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2409187458264581</v>
+        <v>-0.3519066553435537</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.928819113589739</v>
+        <v>-2.116050479068824</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.995673989373489</v>
+        <v>1.883335170086039</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>2.997400223749082</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.351543973969221</v>
+        <v>-8.62901374776196</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1926410696270762</v>
+        <v>-0.4545616996694495</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.796543639958852</v>
+        <v>-1.983775005437937</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.070406760299048</v>
+        <v>1.80713522048632</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.000215284436718</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.160944299296068</v>
+        <v>-8.438414073088806</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1135861390701782</v>
+        <v>-0.3755067691125511</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.605943965285699</v>
+        <v>-1.793175330764784</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.187581625790577</v>
+        <v>1.924310085977848</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.013121625660377</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.911944500612487</v>
+        <v>-8.189414274405225</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.001079878373086984</v>
+        <v>-0.2630005084154603</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.605943965285699</v>
+        <v>-1.793175330764784</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.200487967014236</v>
+        <v>1.937216427201507</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.885145696061159</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.017534490385591</v>
+        <v>-8.295004264178329</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1712918038815476</v>
+        <v>-0.4332124339239205</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.711533955058804</v>
+        <v>-1.898765320537888</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.009158043551154</v>
+        <v>1.745886503738426</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>2.933690037938245</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.036269392504188</v>
+        <v>-8.313739166296926</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1302414228519</v>
+        <v>-0.3921620528942729</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.711533955058804</v>
+        <v>-1.898765320537888</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.05770238542824</v>
+        <v>1.794430845615512</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.813811115250077</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.888329351096589</v>
+        <v>-8.165799124889327</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1909443289770278</v>
+        <v>-0.4528649590194007</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.691213039150246</v>
+        <v>-1.878444404629331</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.950016012285208</v>
+        <v>1.686744472472479</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.805097128996599</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.864100714707616</v>
+        <v>-8.141570488500355</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1899668606749172</v>
+        <v>-0.4518874907172901</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.666984402761274</v>
+        <v>-1.854215768240359</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.955839207865113</v>
+        <v>1.692567668052384</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.798136516901506</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.820552307936926</v>
+        <v>-8.098022081729663</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1795081100617342</v>
+        <v>-0.4414287401041066</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.666984402761274</v>
+        <v>-1.854215768240359</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.94887859577002</v>
+        <v>1.685607055957291</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.812598871282649</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.578403914483068</v>
+        <v>-7.855873688275805</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06818639829904782</v>
+        <v>-0.3301070283414202</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.666984402761274</v>
+        <v>-1.854215768240359</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.963340950151163</v>
+        <v>1.700069410338434</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.807130991741844</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.515174542714719</v>
+        <v>-7.792644316507457</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.04836252913251338</v>
+        <v>-0.3102831591748858</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.666984402761274</v>
+        <v>-1.854215768240359</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.957873070610358</v>
+        <v>1.694601530797629</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.804629085752421</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.391883407897589</v>
+        <v>-7.669353181690326</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.001547981195084258</v>
+        <v>-0.2634686112374567</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.543693267944144</v>
+        <v>-1.730924633423228</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.029345845511213</v>
+        <v>1.766074305698484</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.812330063989746</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.370734208994145</v>
+        <v>-7.648203982786883</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.01461267660361854</v>
+        <v>-0.2473079534387543</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.5225440690407</v>
+        <v>-1.709775434519785</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.049736343090604</v>
+        <v>1.786464803277875</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.808110772336797</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.126968767010701</v>
+        <v>-7.404438540803438</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.107899561744047</v>
+        <v>-0.1540210682983258</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.5225440690407</v>
+        <v>-1.709775434519785</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.045517051437655</v>
+        <v>1.782245511624926</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.810235086256813</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.862940699817441</v>
+        <v>-7.140410473610178</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2156351025413668</v>
+        <v>-0.04628552750100567</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.320678670224747</v>
+        <v>-1.507910035703832</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.168760604647243</v>
+        <v>1.905489064834514</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.802977161240515</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.613090305868367</v>
+        <v>-6.890560079661103</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3083173351046988</v>
+        <v>0.0463967050623264</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.320678670224747</v>
+        <v>-1.507910035703832</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.161502679630945</v>
+        <v>1.898231139818216</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.806576284761164</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.437198213400935</v>
+        <v>-6.714667987193671</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.38227329561232</v>
+        <v>0.1203526655699481</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.320678670224747</v>
+        <v>-1.507910035703832</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.165101803151594</v>
+        <v>1.901830263338865</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.819903790815717</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.265751750378471</v>
+        <v>-6.543221524171208</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4641793868758595</v>
+        <v>0.202258756833487</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.149232207202283</v>
+        <v>-1.336463572681368</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.281297187019625</v>
+        <v>2.018025647206897</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.818924268432014</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.040718750709648</v>
+        <v>-6.318188524502385</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5532130643596855</v>
+        <v>0.2912924343173131</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9241992075334605</v>
+        <v>-1.111430573012545</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.415337464437216</v>
+        <v>2.152065924624488</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.823619069486332</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.826084373073241</v>
+        <v>-6.103554146865978</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6437616164685656</v>
+        <v>0.3818409864261931</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7095648298970537</v>
+        <v>-0.8967961953761385</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.548812892073378</v>
+        <v>2.285541352260649</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.804813328270127</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.733084331867343</v>
+        <v>-6.01055410566008</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6621558917347206</v>
+        <v>0.4002352616923481</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7095648298970537</v>
+        <v>-0.8967961953761385</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.530007150857173</v>
+        <v>2.266735611044445</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.806556404895005</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.492653835062483</v>
+        <v>-5.770123608855219</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7600711670815419</v>
+        <v>0.4981505370391694</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4691343330921934</v>
+        <v>-0.6563656985712782</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.676008525564967</v>
+        <v>2.412736985752238</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.810485718729825</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.420411266891288</v>
+        <v>-5.697881040684025</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7928975081848399</v>
+        <v>0.5309768781424675</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4691343330921934</v>
+        <v>-0.6563656985712782</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.679937839399787</v>
+        <v>2.416666299587058</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.811164302647165</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.304471417266103</v>
+        <v>-5.581941191058839</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.839952031952254</v>
+        <v>0.578031401909882</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3923126020760695</v>
+        <v>-0.5795439675551544</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.726709461926801</v>
+        <v>2.463437922114073</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.808162373867158</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.06181582884294</v>
+        <v>-5.339285602635677</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9340123385415127</v>
+        <v>0.6720917084991402</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3923126020760695</v>
+        <v>-0.5795439675551544</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.723707533146795</v>
+        <v>2.460435993334066</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.809741410877773</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.84179503080593</v>
+        <v>-5.119264804598666</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.023599694766931</v>
+        <v>0.7616790647245586</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2510927570080893</v>
+        <v>-0.4383241224871741</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.810018477198197</v>
+        <v>2.546746937385469</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.825635593679596</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.708927341742652</v>
+        <v>-4.986397115535389</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.092640953194066</v>
+        <v>0.8307203231516931</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2510927570080893</v>
+        <v>-0.4383241224871741</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.82591266000002</v>
+        <v>2.562641120187291</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.826781438119898</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.549412238223282</v>
+        <v>-4.826882012016019</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.157592839042115</v>
+        <v>0.8956722089997429</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.09157765348871938</v>
+        <v>-0.2788090189678042</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.922767566551944</v>
+        <v>2.659496026739216</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.836869540681338</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.404740093123545</v>
+        <v>-4.682209866916281</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.22554979964345</v>
+        <v>0.9636291696010777</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.05309449161101804</v>
+        <v>-0.1341368738680668</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.019658956173227</v>
+        <v>2.756387416360498</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>2.822907032082763</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.464614920481237</v>
+        <v>-4.742084694273974</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.187637360101799</v>
+        <v>0.9257167300594267</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.006780335746674082</v>
+        <v>-0.1940117012257589</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.969771551160037</v>
+        <v>2.706500011347308</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>2.845307525405329</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.377815422702229</v>
+        <v>-4.655285196494965</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.244757652535968</v>
+        <v>0.9828370224935961</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.006780335746674082</v>
+        <v>-0.1940117012257589</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.992172044482603</v>
+        <v>2.728900504669874</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>2.845379926778742</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.380285129164035</v>
+        <v>-4.657754902956771</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.243842171324658</v>
+        <v>0.9819215412822859</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.009250042208480247</v>
+        <v>-0.1964814076875651</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.990762621978932</v>
+        <v>2.727491082166203</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>2.856386849253444</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.448655315488045</v>
+        <v>-4.726125089280782</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.227501019269756</v>
+        <v>0.9655803892273838</v>
       </c>
       <c r="F1936" t="n">
-        <v>2.565682773469913e-05</v>
+        <v>-0.1872057086513501</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.007334963875362</v>
+        <v>2.744063424062634</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>2.846823557885335</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.327238885861568</v>
+        <v>-4.604708659654305</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.266504299752238</v>
+        <v>1.004583669709866</v>
       </c>
       <c r="F1937" t="n">
-        <v>2.565682773469913e-05</v>
+        <v>-0.1872057086513501</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.997771672507254</v>
+        <v>2.734500132694525</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.671533122925722</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.358232045190274</v>
+        <v>-4.63570181898301</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.078816601061143</v>
+        <v>0.8168959710187704</v>
       </c>
       <c r="F1938" t="n">
-        <v>2.565682773469913e-05</v>
+        <v>-0.1872057086513501</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.82248123754764</v>
+        <v>2.559209697734912</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.67610035491751</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.182757785397804</v>
+        <v>-4.460227559190541</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.153573536969918</v>
+        <v>0.8916529069275461</v>
       </c>
       <c r="F1939" t="n">
-        <v>2.565682773469913e-05</v>
+        <v>-0.1872057086513501</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.827048469539428</v>
+        <v>2.5637769297267</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>2.651842383678717</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.293694038039053</v>
+        <v>-4.57116381183179</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.084941064674626</v>
+        <v>0.8230204346322534</v>
       </c>
       <c r="F1940" t="n">
-        <v>2.565682773469913e-05</v>
+        <v>-0.1872057086513501</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.802790498300635</v>
+        <v>2.539518958487907</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.654973768898622</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.496720615582286</v>
+        <v>-4.774190389375023</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.006861818877238</v>
+        <v>0.7449411888348658</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2030009207154987</v>
+        <v>-0.3902322861945835</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.684105936994601</v>
+        <v>2.420834397181872</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>2.665146155330754</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.338795016646993</v>
+        <v>-4.61626479043973</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.080204444883488</v>
+        <v>0.8182838148411153</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2030009207154987</v>
+        <v>-0.3902322861945835</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.694278323426733</v>
+        <v>2.431006783614005</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.660092425904615</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.252551553620616</v>
+        <v>-4.530021327413352</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.109648100667899</v>
+        <v>0.8477274706255267</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2030009207154987</v>
+        <v>-0.3902322861945835</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.689224594000593</v>
+        <v>2.425953054187865</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.65186820134914</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.253734638271677</v>
+        <v>-4.531204412064413</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.100950642252</v>
+        <v>0.8390300122096277</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2086439691820102</v>
+        <v>-0.395875334661095</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.677614540365212</v>
+        <v>2.414343000552484</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.652420074382242</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.130606931277594</v>
+        <v>-4.40807670507033</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.150753598082735</v>
+        <v>0.8888329680403624</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2086439691820102</v>
+        <v>-0.395875334661095</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.678166413398314</v>
+        <v>2.414894873585585</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.581692766273608</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.037796449826734</v>
+        <v>-4.315266223619471</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.117150482554444</v>
+        <v>0.8552298525120721</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1158334877311509</v>
+        <v>-0.3030648532102357</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.663125394160195</v>
+        <v>2.399853854347466</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.583566242198208</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.989233397605704</v>
+        <v>-4.266703171398441</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.138449179367457</v>
+        <v>0.8765285493250847</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.06727043551012069</v>
+        <v>-0.2545018009892055</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.694136701417414</v>
+        <v>2.430865161604685</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.578641950709931</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.876562179369454</v>
+        <v>-4.154031953162191</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.17859337517368</v>
+        <v>0.9166727451313079</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.04540078272612952</v>
+        <v>-0.1418305827529553</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.756815140870887</v>
+        <v>2.493543601058159</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.584133246540599</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.764185178186781</v>
+        <v>-4.041654951979518</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.229035471477417</v>
+        <v>0.9671148414350443</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.04540078272612952</v>
+        <v>-0.1418305827529553</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.762306436701554</v>
+        <v>2.499034896888826</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.595630448309138</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.962419747073512</v>
+        <v>-4.239889520866249</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.161238845691263</v>
+        <v>0.899318215648891</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1528337861606011</v>
+        <v>-0.3400651516396859</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.654862897138055</v>
+        <v>2.391591357325326</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.433986168309791</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.04542102809879</v>
+        <v>-4.322890801891528</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9663940532818054</v>
+        <v>0.7044734232394327</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1714046706877748</v>
+        <v>-0.3586360361668596</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.482076086422404</v>
+        <v>2.218804546609675</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.554135829028997</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.886226756042214</v>
+        <v>-4.163696529834951</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.150221422823642</v>
+        <v>0.8883007927812689</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1714046706877748</v>
+        <v>-0.3586360361668596</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.60222574714161</v>
+        <v>2.338954207328881</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.56864885513132</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.972825339023317</v>
+        <v>-4.250295112816054</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.130095015733523</v>
+        <v>0.8681743856911508</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1714046706877748</v>
+        <v>-0.3586360361668596</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.616738773243933</v>
+        <v>2.353467233431204</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.566068296473688</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.934441676465166</v>
+        <v>-4.211911450257903</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.142867922099152</v>
+        <v>0.88094729205678</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1330210081296236</v>
+        <v>-0.3202523736087085</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.637188412121192</v>
+        <v>2.373916872308464</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.56279732531899</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.75732534643</v>
+        <v>-4.034795120222737</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.210443482958521</v>
+        <v>0.9485228529161482</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1330210081296236</v>
+        <v>-0.3202523736087085</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.633917440966494</v>
+        <v>2.370645901153766</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.563480717080903</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.727623222453706</v>
+        <v>-4.005092996246443</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.223007724310951</v>
+        <v>0.9610870942685787</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.137491133344937</v>
+        <v>-0.3247224988240218</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.631918757599219</v>
+        <v>2.36864721778649</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.557267692387318</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.548247801214938</v>
+        <v>-3.825717575007675</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.288544868112873</v>
+        <v>1.0266242380705</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.01928562482578167</v>
+        <v>-0.1679457406533031</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.719771787808065</v>
+        <v>2.456500247995336</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.538075147718907</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.593262014735544</v>
+        <v>-3.870731788528281</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.25134663803622</v>
+        <v>0.9894260079938475</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.01106327048882294</v>
+        <v>-0.1982946359679078</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.682369905950892</v>
+        <v>2.419098366138163</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.543766710057853</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.86026652500798</v>
+        <v>-4.137736298800717</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.150236396266192</v>
+        <v>0.888315766223819</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2054263085317715</v>
+        <v>-0.3926576740108563</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.571443645464068</v>
+        <v>2.30817210565134</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.542970631954355</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.149053745466895</v>
+        <v>-4.426523519259632</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.033925429979127</v>
+        <v>0.7720047999367545</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3065124286307719</v>
+        <v>-0.4937437941098567</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.50999589530117</v>
+        <v>2.246724355488441</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>2.540570593508671</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.116578159296123</v>
+        <v>-4.39404793308886</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.044515626001753</v>
+        <v>0.7825949959593801</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3065124286307719</v>
+        <v>-0.4937437941098567</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.507595856855486</v>
+        <v>2.244324317042758</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.854529328865257</v>
+        <v>3.430089877763904</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.871987752641979</v>
+        <v>2.716668638288986</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.116578159296123</v>
+        <v>-4.330024553437673</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.044515626001753</v>
+        <v>0.9843023926001693</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3065124286307719</v>
+        <v>-0.5700048029169024</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.865051549628347</v>
+        <v>2.374665756538845</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240512.xlsx
+++ b/tame_output/ON/bt/strategyON_20240512.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-42.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-53.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.8%</t>
+          <t>439.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.6%</t>
+          <t>-591.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-279.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.0%</t>
+          <t>-117.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-281.0%</t>
+          <t>-270.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-208.6%</t>
+          <t>-205.0%</t>
         </is>
       </c>
     </row>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355691</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760745</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.54142628370588</v>
+        <v>-10.44295392890647</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.059646145884569</v>
+        <v>-1.020257203964801</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.564261804081802</v>
+        <v>-2.465789449282382</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.618723709462451</v>
+        <v>1.677807122342103</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.71655070109243</v>
+        <v>-10.61807834629301</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.11514069209167</v>
+        <v>-1.075751750171902</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.739386221468346</v>
+        <v>-2.640913866668926</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.528204279778042</v>
+        <v>1.587287692657693</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.95100279510692</v>
+        <v>-10.8525304403075</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.216140694599062</v>
+        <v>-1.176751752679294</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.739386221468346</v>
+        <v>-2.640913866668926</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.520985114876445</v>
+        <v>1.580068527756097</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.23880663964416</v>
+        <v>-11.14033428484474</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.337934423187934</v>
+        <v>-1.298545481268166</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.027190066005584</v>
+        <v>-2.928717711206164</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.341630617380126</v>
+        <v>1.400714030259778</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.46863108680798</v>
+        <v>-11.37015873200856</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.428748412214907</v>
+        <v>-1.38935947029514</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.189837603075745</v>
+        <v>-3.091365248276325</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.245157884976587</v>
+        <v>1.304241297856238</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.70066000654424</v>
+        <v>-11.60218765174482</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.518866251480298</v>
+        <v>-1.47947730956053</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.251850300264168</v>
+        <v>-3.153377945464748</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.210643995292647</v>
+        <v>1.269727408172299</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.64864449257543</v>
+        <v>-11.55017213777601</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.494069710206371</v>
+        <v>-1.454680768286603</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.251850300264168</v>
+        <v>-3.153377945464748</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.214634330979048</v>
+        <v>1.2737177438587</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.79031633429955</v>
+        <v>-11.69184397950013</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.55221367379476</v>
+        <v>-1.512824731874993</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.251850300264168</v>
+        <v>-3.153377945464748</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.213159104080306</v>
+        <v>1.272242516959958</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.74072548987472</v>
+        <v>-11.6422531350753</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.517323925859955</v>
+        <v>-1.477934983940187</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.202259455839334</v>
+        <v>-3.103787101039914</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.257967020900079</v>
+        <v>1.317050433779731</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.54157338263762</v>
+        <v>-11.4431010278382</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.450714216611798</v>
+        <v>-1.41132527469203</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.036936929889521</v>
+        <v>-2.938464575090101</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.344109402823284</v>
+        <v>1.403192815702936</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.31572822991821</v>
+        <v>-11.21725587511879</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.350797082487826</v>
+        <v>-1.311408140568058</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.995010254302357</v>
+        <v>-2.896537899502937</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.378844481211791</v>
+        <v>1.437927894091443</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.19114957358062</v>
+        <v>-11.0926772187812</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.29982647539673</v>
+        <v>-1.260437533476962</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.995010254302357</v>
+        <v>-2.896537899502937</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.379983625767849</v>
+        <v>1.439067038647502</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.2440448616249</v>
+        <v>-11.14557250682548</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.318350816452337</v>
+        <v>-1.278961874532569</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.990054908213911</v>
+        <v>-2.891582553414491</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.385590607583025</v>
+        <v>1.444674020462677</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.96013613069615</v>
+        <v>-10.86166377589673</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.199053619842201</v>
+        <v>-1.159664677922433</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.990054908213911</v>
+        <v>-2.891582553414491</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.391324311821661</v>
+        <v>1.450407724701313</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.88876973808651</v>
+        <v>-10.79029738328709</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.180244325192207</v>
+        <v>-1.14085538327244</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.918688515604263</v>
+        <v>-2.820216160804843</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.424406884993585</v>
+        <v>1.483490297873237</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.62493287088244</v>
+        <v>-10.52646051608302</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.084593059623487</v>
+        <v>-1.045204117703719</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.918688515604263</v>
+        <v>-2.820216160804843</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.414523403680677</v>
+        <v>1.473606816560329</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.35769107001404</v>
+        <v>-10.25921871521462</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9795308997755012</v>
+        <v>-0.9401419578557335</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.918688515604263</v>
+        <v>-2.820216160804843</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.412688843181304</v>
+        <v>1.471772256060956</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.25978403133755</v>
+        <v>-10.16131167653813</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.940668399278366</v>
+        <v>-0.9012794573585983</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.850702765743707</v>
+        <v>-2.752230410944287</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.453179978124177</v>
+        <v>1.512263391003829</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.23583049036159</v>
+        <v>-10.13735813556217</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.930418476742489</v>
+        <v>-0.8910295348227213</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.826749224767749</v>
+        <v>-2.728276869968329</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.468220608855245</v>
+        <v>1.527304021734897</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.971770552038793</v>
+        <v>-9.873298197239373</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8380548175751228</v>
+        <v>-0.7986658756553551</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.562689286444953</v>
+        <v>-2.464216931645533</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.61339625568717</v>
+        <v>1.672479668566822</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.264690928533955</v>
+        <v>-9.166218573734536</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5580100018334884</v>
+        <v>-0.5186210599137207</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.562689286444953</v>
+        <v>-2.464216931645533</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.610609222026869</v>
+        <v>1.669692634906521</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.224506630167765</v>
+        <v>-9.126034275368346</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5415926585991708</v>
+        <v>-0.5022037166794031</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.522504988078762</v>
+        <v>-2.424032633279342</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.635063424934425</v>
+        <v>1.694146837814077</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.14443683462996</v>
+        <v>-9.045964479830541</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5101979191632924</v>
+        <v>-0.4708089772435247</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.442435192540958</v>
+        <v>-2.343962837741538</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.682472123477865</v>
+        <v>1.741555536357517</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.910955612400361</v>
+        <v>-8.812483257600942</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4088810014336</v>
+        <v>-0.3694920595138322</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.20895397031136</v>
+        <v>-2.11048161551194</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.830485285653476</v>
+        <v>1.889568698533128</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.761289221392847</v>
+        <v>-8.662816866593428</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3519066553435537</v>
+        <v>-0.312517713423786</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.116050479068824</v>
+        <v>-2.017578124269404</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.883335170086039</v>
+        <v>1.942418582965691</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
-        <v>2.997400223749082</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.62901374776196</v>
+        <v>-8.53054139296254</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4545616996694495</v>
+        <v>-0.264240037224404</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.983775005437937</v>
+        <v>-1.885302650638517</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.80713522048632</v>
+        <v>2.01715135389125</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.000215284436718</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.438414073088806</v>
+        <v>-8.339941718289387</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3755067691125511</v>
+        <v>-0.1851851066675057</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.793175330764784</v>
+        <v>-1.694702975965364</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.924310085977848</v>
+        <v>2.134326219382778</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.013121625660377</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.189414274405225</v>
+        <v>-8.090941919605806</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2630005084154603</v>
+        <v>-0.07267884597041485</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.793175330764784</v>
+        <v>-1.694702975965364</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.937216427201507</v>
+        <v>2.147232560606437</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.885145696061159</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.295004264178329</v>
+        <v>-8.19653190937891</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4332124339239205</v>
+        <v>-0.2428907714788751</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.898765320537888</v>
+        <v>-1.800292965738468</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.745886503738426</v>
+        <v>1.955902637143356</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.933690037938245</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.313739166296926</v>
+        <v>-8.215266811497507</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3921620528942729</v>
+        <v>-0.2018403904492274</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.898765320537888</v>
+        <v>-1.800292965738468</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.794430845615512</v>
+        <v>2.004446979020442</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.813811115250077</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.165799124889327</v>
+        <v>-8.067326770089908</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4528649590194007</v>
+        <v>-0.2625432965743553</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.878444404629331</v>
+        <v>-1.779972049829911</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.686744472472479</v>
+        <v>1.896760605877409</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.805097128996599</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.141570488500355</v>
+        <v>-8.043098133700935</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4518874907172901</v>
+        <v>-0.2615658282722446</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.854215768240359</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.692567668052384</v>
+        <v>1.902583801457314</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.798136516901506</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.098022081729663</v>
+        <v>-7.999549726930245</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4414287401041066</v>
+        <v>-0.2511070776590616</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.854215768240359</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.685607055957291</v>
+        <v>1.895623189362221</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.812598871282649</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.855873688275805</v>
+        <v>-7.757401333476387</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3301070283414202</v>
+        <v>-0.1397853658963752</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.854215768240359</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.700069410338434</v>
+        <v>1.910085543743364</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.807130991741844</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.792644316507457</v>
+        <v>-7.694171961708038</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3102831591748858</v>
+        <v>-0.1199614967298408</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.854215768240359</v>
+        <v>-1.755743413440939</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.694601530797629</v>
+        <v>1.904617664202559</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.804629085752421</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.669353181690326</v>
+        <v>-7.570880826890908</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2634686112374567</v>
+        <v>-0.07314694879241168</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.730924633423228</v>
+        <v>-1.632452278623808</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.766074305698484</v>
+        <v>1.976090439103414</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.812330063989746</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.648203982786883</v>
+        <v>-7.549731627987464</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2473079534387543</v>
+        <v>-0.05698629099370933</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.709775434519785</v>
+        <v>-1.611303079720365</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.786464803277875</v>
+        <v>1.996480936682805</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.808110772336797</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.404438540803438</v>
+        <v>-7.30596618600402</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1540210682983258</v>
+        <v>0.03630059414671916</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.709775434519785</v>
+        <v>-1.611303079720365</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.782245511624926</v>
+        <v>1.992261645029856</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.810235086256813</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.140410473610178</v>
+        <v>-7.04193811881076</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.04628552750100567</v>
+        <v>0.1440361349440389</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.507910035703832</v>
+        <v>-1.409437680904411</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.905489064834514</v>
+        <v>2.115505198239444</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.802977161240515</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.890560079661103</v>
+        <v>-6.792087724861686</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0463967050623264</v>
+        <v>0.236718367507371</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.507910035703832</v>
+        <v>-1.409437680904411</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.898231139818216</v>
+        <v>2.108247273223146</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.806576284761164</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.714667987193671</v>
+        <v>-6.616195632394254</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1203526655699481</v>
+        <v>0.3106743280149926</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.507910035703832</v>
+        <v>-1.409437680904411</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.901830263338865</v>
+        <v>2.111846396743795</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.819903790815717</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.543221524171208</v>
+        <v>-6.44474916937179</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.202258756833487</v>
+        <v>0.3925804192785316</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.336463572681368</v>
+        <v>-1.237991217881948</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.018025647206897</v>
+        <v>2.228041780611826</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.818924268432014</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.318188524502385</v>
+        <v>-6.219716169702967</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2912924343173131</v>
+        <v>0.4816140967623577</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.111430573012545</v>
+        <v>-1.012958218213125</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.152065924624488</v>
+        <v>2.362082058029417</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.823619069486332</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.103554146865978</v>
+        <v>-6.00508179206656</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3818409864261931</v>
+        <v>0.5721626488712381</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8967961953761385</v>
+        <v>-0.7983238405767183</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.285541352260649</v>
+        <v>2.495557485665579</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.804813328270127</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.01055410566008</v>
+        <v>-5.912081750860662</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4002352616923481</v>
+        <v>0.5905569241373927</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8967961953761385</v>
+        <v>-0.7983238405767183</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.266735611044445</v>
+        <v>2.476751744449374</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.806556404895005</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.770123608855219</v>
+        <v>-5.671651254055802</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4981505370391694</v>
+        <v>0.6884721994842145</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6563656985712782</v>
+        <v>-0.5578933437718581</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.412736985752238</v>
+        <v>2.622753119157168</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.810485718729825</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.697881040684025</v>
+        <v>-5.599408685884607</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5309768781424675</v>
+        <v>0.7212985405875125</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6563656985712782</v>
+        <v>-0.5578933437718581</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.416666299587058</v>
+        <v>2.626682432991988</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.811164302647165</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.581941191058839</v>
+        <v>-5.483468836259422</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.578031401909882</v>
+        <v>0.7683530643549266</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5795439675551544</v>
+        <v>-0.4810716127557342</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.463437922114073</v>
+        <v>2.673454055519002</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.808162373867158</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.339285602635677</v>
+        <v>-5.240813247836259</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6720917084991402</v>
+        <v>0.8624133709441852</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5795439675551544</v>
+        <v>-0.4810716127557342</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.460435993334066</v>
+        <v>2.670452126738996</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.809741410877773</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.119264804598666</v>
+        <v>-5.020792449799249</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7616790647245586</v>
+        <v>0.9520007271696036</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4383241224871741</v>
+        <v>-0.3398517676877539</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.546746937385469</v>
+        <v>2.756763070790398</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.825635593679596</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.986397115535389</v>
+        <v>-4.887924760735971</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8307203231516931</v>
+        <v>1.021041985596738</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4383241224871741</v>
+        <v>-0.3398517676877539</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.562641120187291</v>
+        <v>2.772657253592222</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.826781438119898</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.826882012016019</v>
+        <v>-4.728409657216601</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8956722089997429</v>
+        <v>1.085993871444788</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2788090189678042</v>
+        <v>-0.180336664168384</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.659496026739216</v>
+        <v>2.869512160144145</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.836869540681338</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.682209866916281</v>
+        <v>-4.583737512116864</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9636291696010777</v>
+        <v>1.153950832046122</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1341368738680668</v>
+        <v>-0.03566451906864659</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.756387416360498</v>
+        <v>2.966403549765428</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412105</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.822907032082763</v>
+        <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.742084694273974</v>
+        <v>-4.643612339474556</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9257167300594267</v>
+        <v>1.116038392504471</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1940117012257589</v>
+        <v>-0.09553934642633871</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.706500011347308</v>
+        <v>2.916516144752238</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.845307525405329</v>
+        <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.655285196494965</v>
+        <v>-4.556812841695548</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9828370224935961</v>
+        <v>1.173158684938641</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1940117012257589</v>
+        <v>-0.09553934642633871</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.728900504669874</v>
+        <v>2.938916638074804</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.845379926778742</v>
+        <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.657754902956771</v>
+        <v>-4.559282548157354</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9819215412822859</v>
+        <v>1.17224320372733</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1964814076875651</v>
+        <v>-0.09800905288814488</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.727491082166203</v>
+        <v>2.937507215571133</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.856386849253444</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.726125089280782</v>
+        <v>-4.627652734481364</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9655803892273838</v>
+        <v>1.155902051672429</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1872057086513501</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.744063424062634</v>
+        <v>2.954079557467564</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.846823557885335</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.604708659654305</v>
+        <v>-4.506236304854887</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.004583669709866</v>
+        <v>1.19490533215491</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1872057086513501</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.734500132694525</v>
+        <v>2.944516266099455</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.671533122925722</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.63570181898301</v>
+        <v>-4.537229464183593</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8168959710187704</v>
+        <v>1.007217633463815</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1872057086513501</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.559209697734912</v>
+        <v>2.769225831139842</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.67610035491751</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.460227559190541</v>
+        <v>-4.361755204391123</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8916529069275461</v>
+        <v>1.081974569372591</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1872057086513501</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.5637769297267</v>
+        <v>2.77379306313163</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.651842383678717</v>
+        <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.57116381183179</v>
+        <v>-4.472691457032372</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8230204346322534</v>
+        <v>1.013342097077298</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1872057086513501</v>
+        <v>-0.08873335385192993</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.539518958487907</v>
+        <v>2.749535091892837</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.654973768898622</v>
+        <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.774190389375023</v>
+        <v>-4.675718034575605</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7449411888348658</v>
+        <v>0.9352628512799104</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3902322861945835</v>
+        <v>-0.2917599313951633</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.420834397181872</v>
+        <v>2.630850530586802</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.665146155330754</v>
+        <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.61626479043973</v>
+        <v>-4.517792435640312</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8182838148411153</v>
+        <v>1.00860547728616</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3902322861945835</v>
+        <v>-0.2917599313951633</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.431006783614005</v>
+        <v>2.641022917018935</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.660092425904615</v>
+        <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.530021327413352</v>
+        <v>-4.431548972613935</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8477274706255267</v>
+        <v>1.038049133070571</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3902322861945835</v>
+        <v>-0.2917599313951633</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.425953054187865</v>
+        <v>2.635969187592795</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.65186820134914</v>
+        <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.531204412064413</v>
+        <v>-4.432732057264996</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8390300122096277</v>
+        <v>1.029351674654672</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.395875334661095</v>
+        <v>-0.2974029798616749</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.414343000552484</v>
+        <v>2.624359133957413</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.652420074382242</v>
+        <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.40807670507033</v>
+        <v>-4.381075782540919</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8888329680403624</v>
+        <v>1.050566057577405</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.395875334661095</v>
+        <v>-0.2974029798616749</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.414894873585585</v>
+        <v>2.624911006990515</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.581692766273608</v>
+        <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.315266223619471</v>
+        <v>-4.28826530109006</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8552298525120721</v>
+        <v>1.016962942049114</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3030648532102357</v>
+        <v>-0.2045924984108155</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.399853854347466</v>
+        <v>2.609869987752396</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.583566242198208</v>
+        <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.266703171398441</v>
+        <v>-4.23970224886903</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8765285493250847</v>
+        <v>1.038261638862127</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2545018009892055</v>
+        <v>-0.1560294461897853</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.430865161604685</v>
+        <v>2.640881295009615</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.578641950709931</v>
+        <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.154031953162191</v>
+        <v>-4.12703103063278</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9166727451313079</v>
+        <v>1.07840583466835</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1418305827529553</v>
+        <v>-0.04335822795353511</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.493543601058159</v>
+        <v>2.703559734463088</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.584133246540599</v>
+        <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.041654951979518</v>
+        <v>-4.014654029450107</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9671148414350443</v>
+        <v>1.128847930972086</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1418305827529553</v>
+        <v>-0.04335822795353511</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.499034896888826</v>
+        <v>2.709051030293756</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.595630448309138</v>
+        <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.239889520866249</v>
+        <v>-4.212888598336837</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.899318215648891</v>
+        <v>1.061051305185933</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3400651516396859</v>
+        <v>-0.2415927968402657</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.391591357325326</v>
+        <v>2.601607490730256</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.433986168309791</v>
+        <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.322890801891528</v>
+        <v>-4.295889879362116</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7044734232394327</v>
+        <v>0.8662065127764749</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3586360361668596</v>
+        <v>-0.2601636813674394</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.218804546609675</v>
+        <v>2.428820680014605</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.554135829028997</v>
+        <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.163696529834951</v>
+        <v>-4.136695607305541</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8883007927812689</v>
+        <v>1.050033882318311</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3586360361668596</v>
+        <v>-0.2601636813674394</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.338954207328881</v>
+        <v>2.548970340733811</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.56864885513132</v>
+        <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.250295112816054</v>
+        <v>-4.223294190286643</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8681743856911508</v>
+        <v>1.029907475228193</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3586360361668596</v>
+        <v>-0.2601636813674394</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.353467233431204</v>
+        <v>2.563483366836134</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.566068296473688</v>
+        <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.211911450257903</v>
+        <v>-4.184910527728492</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.88094729205678</v>
+        <v>1.042680381593822</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3202523736087085</v>
+        <v>-0.2217800188092883</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.373916872308464</v>
+        <v>2.583933005713393</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.56279732531899</v>
+        <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.034795120222737</v>
+        <v>-4.007794197693326</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9485228529161482</v>
+        <v>1.11025594245319</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3202523736087085</v>
+        <v>-0.2217800188092883</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.370645901153766</v>
+        <v>2.580662034558695</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.563480717080903</v>
+        <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.005092996246443</v>
+        <v>-3.978092073717033</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9610870942685787</v>
+        <v>1.122820183805621</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3247224988240218</v>
+        <v>-0.2262501440246016</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.36864721778649</v>
+        <v>2.578663351191421</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.557267692387318</v>
+        <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.825717575007675</v>
+        <v>-3.798716652478265</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.0266242380705</v>
+        <v>1.188357327607542</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1679457406533031</v>
+        <v>-0.06947338585388296</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.456500247995336</v>
+        <v>2.666516381400266</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.538075147718907</v>
+        <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.870731788528281</v>
+        <v>-3.843730865998871</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9894260079938475</v>
+        <v>1.151159097530889</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1982946359679078</v>
+        <v>-0.09982228116848757</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.419098366138163</v>
+        <v>2.629114499543093</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.543766710057853</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.137736298800717</v>
+        <v>-4.110735376271307</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.888315766223819</v>
+        <v>1.050048855760861</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3926576740108563</v>
+        <v>-0.2941853192114361</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.30817210565134</v>
+        <v>2.518188239056269</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.542970631954355</v>
+        <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.426523519259632</v>
+        <v>-4.399522596730222</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7720047999367545</v>
+        <v>0.9337378894737962</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4937437941098567</v>
+        <v>-0.3952714393104365</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.246724355488441</v>
+        <v>2.456740488893371</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.540570593508671</v>
+        <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.39404793308886</v>
+        <v>-4.36704701055945</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7825949959593801</v>
+        <v>0.944328085496422</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4937437941098567</v>
+        <v>-0.3952714393104365</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.244324317042758</v>
+        <v>2.454340450447687</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.430089877763904</v>
+        <v>3.427188187775672</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.716668638288986</v>
+        <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.330024553437673</v>
+        <v>-4.294029488511038</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9843023926001693</v>
+        <v>0.9700598135240315</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5700048029169024</v>
+        <v>-0.4636180433711736</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.374665756538845</v>
+        <v>2.40985720721949</v>
       </c>
     </row>
   </sheetData>
